--- a/Excel/IED_FBKF_7.xlsx
+++ b/Excel/IED_FBKF_7.xlsx
@@ -1,36 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\BL6PEPF000466DC\EXCELCNV\ff0aa13c-695e-4c15-9ace-b4a18c47a150\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonathan.barboza\Documents\Temas DGIE\Materiales reporte trimestral\Indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{874B24F3-D32F-4735-B269-58132CC3F05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2907F3B5-3F4B-4E49-8307-6D2CF70D2584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{05F2D8F3-5A28-4627-AC6D-5687CA2AE1CE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IED_FBKF_Trimestral" sheetId="1" r:id="rId1"/>
-    <sheet name="IED_FBKF_Anual" sheetId="2" r:id="rId2"/>
-    <sheet name="Metodología" sheetId="3" r:id="rId3"/>
+    <sheet name="IED_FBCF_Trimestral" sheetId="1" r:id="rId1"/>
+    <sheet name="IED_FBCF_Anual" sheetId="2" r:id="rId2"/>
+    <sheet name="Metodología" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_ftn1" localSheetId="2">Metodología!$A$28</definedName>
-    <definedName name="_ftn2" localSheetId="2">Metodología!$A$29</definedName>
-    <definedName name="_ftnref1" localSheetId="2">Metodología!$A$2</definedName>
-    <definedName name="_ftnref2" localSheetId="2">Metodología!$A$12</definedName>
     <definedName name="A">#N/A</definedName>
     <definedName name="A_impresión_IM" localSheetId="1">#REF!</definedName>
     <definedName name="A_impresión_IM">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -47,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="18">
-  <si>
-    <t>FLUJOS DE IED COMO PORCENTAJE DE LA FORMACIÓN BRUTA DE CAPITAL FIJO TRIMESTRAL*/</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="18">
   <si>
     <t>Año</t>
   </si>
@@ -61,13 +51,10 @@
     <t>IED*/</t>
   </si>
   <si>
-    <t>FBKF</t>
+    <t>FBCF</t>
   </si>
   <si>
-    <t>IED/FBKF</t>
-  </si>
-  <si>
-    <t>Millones de dólares corrientes</t>
+    <t>IED/FBCF</t>
   </si>
   <si>
     <t>Porcentaje</t>
@@ -85,22 +72,28 @@
     <t>IV</t>
   </si>
   <si>
-    <t>*/ Con información al 31 de diciembre de 2025.</t>
-  </si>
-  <si>
-    <t>Fuente: Secretaría de Economía, INEGI y Banco de México.</t>
-  </si>
-  <si>
-    <t>Nota metodológica: Las cifras referentes a la IED y a la FBKF se presentan en dólares. La Secretaría de Economía realiza la conversión de la FBKF trimestral utilizando el tipo de cambio FIX publicado por el Banco de México, en promedio por cada trimestre. Asimismo, la FBKF trimestral se presenta anualizada en la fuente original, por lo cual se desanualiza para dimesionar la participación del flujo trimestral de la IED.</t>
-  </si>
-  <si>
-    <t>FLUJOS DE IED COMO PORCENTAJE DE LA FORMACIÓN BRUTA DE CAPITAL FIJO ANUAL*/</t>
-  </si>
-  <si>
     <t>IED</t>
   </si>
   <si>
-    <t>Nota metodológica: Las cifras referentes a la IED y a la FBKF se presentan en dólares. La Secretaría de Economía realiza el calculo de la FBKF a partir del promedio simple de la FBKF trimestral anualizada, expresada en dólares americanos utilizando el tipo de cambio FIX publicado por el Banco de México.</t>
+    <t>Millones de dólares corrientes</t>
+  </si>
+  <si>
+    <t>Fuente: Secretaría de Economía, INEGI y Banco de México. Información actualizada al 30 de junio de 2026.</t>
+  </si>
+  <si>
+    <t>Nota metodológica 2: Los flujos de IED previos al año 2006 no se encuentran sujetos a nuevas actualizaciones.</t>
+  </si>
+  <si>
+    <t>Nota metodológica 1:  Las cifras referentes a la IED y a la FBCF se expresan en dólares corrientes, para lo cual la Secretaría de Economía realiza la conversión de la FBCF utilizando el promedio trimestral del tipo de cambio FIX. Asimismo, los datos de la FBCF anualizada presentados por el INEGI se dividieron entre cuatro para expresarlos en niveles trimestrales, con lo cual se facilita la comparación con los flujos trimestrales de IED.</t>
+  </si>
+  <si>
+    <t>Nota metodológica 1:  Las cifras referentes a la IED y a la FBCF se expresan en dólares corrientes, para lo cual la Secretaría de Economía realiza la conversión de la FBCF utilizando el promedio anual del tipo de cambio FIX.</t>
+  </si>
+  <si>
+    <t>FLUJOS DE IED COMO PORCENTAJE DE LA FORMACIÓN BRUTA DE CAPITAL FIJO TRIMESTRAL ANUALIZADO</t>
+  </si>
+  <si>
+    <t>FLUJOS DE IED COMO PORCENTAJE DE LA FORMACIÓN BRUTA DE CAPITAL FIJO ANUAL</t>
   </si>
 </sst>
 </file>
@@ -111,13 +104,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -128,6 +115,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Noto Sans"/>
       <family val="2"/>
     </font>
     <font>
@@ -156,10 +150,9 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="0"/>
-      <name val="Noto Sans"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -308,7 +301,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -343,17 +338,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -361,129 +345,127 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -497,88 +479,85 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{D862A6EC-19F1-4467-ACDE-CEC909D8B9FE}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{9F51EC95-695F-4D13-BFC3-6B3BE6C15557}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -596,7 +575,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -614,8 +593,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.1466596675415572E-2"/>
-          <c:y val="7.8142311781617235E-2"/>
+          <c:x val="2.146657134131625E-2"/>
+          <c:y val="7.9909384853896231E-2"/>
           <c:w val="0.9529975185533619"/>
           <c:h val="0.77020551601873588"/>
         </c:manualLayout>
@@ -653,7 +632,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-721E-459A-8DE9-A55E5DF6330D}"/>
+                <c16:uniqueId val="{00000000-A430-4475-8715-BC0EAEF83F89}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -663,7 +642,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-721E-459A-8DE9-A55E5DF6330D}"/>
+                <c16:uniqueId val="{00000001-A430-4475-8715-BC0EAEF83F89}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -672,33 +651,10 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="3.555137274837515E-3"/>
-                  <c:y val="0"/>
+                  <c:x val="3.5551550524729426E-3"/>
+                  <c:y val="-2.2972422796101514E-2"/>
                 </c:manualLayout>
               </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln w="25400">
-                  <a:noFill/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans"/>
-                      <a:ea typeface="Noto Sans"/>
-                      <a:cs typeface="Noto Sans"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
               <c:dLblPos val="outEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -709,7 +665,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-721E-459A-8DE9-A55E5DF6330D}"/>
+                  <c16:uniqueId val="{00000002-A430-4475-8715-BC0EAEF83F89}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -717,34 +673,10 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-3.2797747256673116E-18"/>
-                  <c:y val="4.5792784884006038E-3"/>
+                  <c:x val="6.8007936686859713E-4"/>
+                  <c:y val="0"/>
                 </c:manualLayout>
               </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln w="25400">
-                  <a:noFill/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans"/>
-                      <a:ea typeface="Noto Sans"/>
-                      <a:cs typeface="Noto Sans"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -754,42 +686,18 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-721E-459A-8DE9-A55E5DF6330D}"/>
+                  <c16:uniqueId val="{00000002-FE66-4E25-B0A0-E0B5B3E3692F}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="11"/>
+              <c:idx val="5"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-1.4311909587948291E-3"/>
-                  <c:y val="0"/>
+                  <c:x val="0"/>
+                  <c:y val="-7.0684377834157658E-3"/>
                 </c:manualLayout>
               </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln w="25400">
-                  <a:noFill/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans"/>
-                      <a:ea typeface="Noto Sans"/>
-                      <a:cs typeface="Noto Sans"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -799,42 +707,18 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-721E-459A-8DE9-A55E5DF6330D}"/>
+                  <c16:uniqueId val="{00000003-FE66-4E25-B0A0-E0B5B3E3692F}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="41"/>
+              <c:idx val="13"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="3.5779773969870201E-3"/>
-                  <c:y val="3.0528523256004021E-3"/>
+                  <c:x val="-6.8007936686860027E-4"/>
+                  <c:y val="-6.4793264517324391E-17"/>
                 </c:manualLayout>
               </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln w="25400">
-                  <a:noFill/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans"/>
-                      <a:ea typeface="Noto Sans"/>
-                      <a:cs typeface="Noto Sans"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -844,42 +728,18 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-721E-459A-8DE9-A55E5DF6330D}"/>
+                  <c16:uniqueId val="{00000004-FE66-4E25-B0A0-E0B5B3E3692F}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="44"/>
+              <c:idx val="14"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-3.577977396987125E-3"/>
-                  <c:y val="-5.5968312751949165E-17"/>
+                  <c:x val="0"/>
+                  <c:y val="3.5342188917078508E-3"/>
                 </c:manualLayout>
               </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln w="25400">
-                  <a:noFill/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans"/>
-                      <a:ea typeface="Noto Sans"/>
-                      <a:cs typeface="Noto Sans"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -889,42 +749,18 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-721E-459A-8DE9-A55E5DF6330D}"/>
+                  <c16:uniqueId val="{00000006-FE66-4E25-B0A0-E0B5B3E3692F}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="45"/>
+              <c:idx val="15"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="5.0091683557819018E-3"/>
-                  <c:y val="3.0528523256002902E-3"/>
+                  <c:x val="3.4003968343429762E-3"/>
+                  <c:y val="0"/>
                 </c:manualLayout>
               </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln w="25400">
-                  <a:noFill/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans"/>
-                      <a:ea typeface="Noto Sans"/>
-                      <a:cs typeface="Noto Sans"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -934,42 +770,18 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-721E-459A-8DE9-A55E5DF6330D}"/>
+                  <c16:uniqueId val="{00000005-FE66-4E25-B0A0-E0B5B3E3692F}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="90"/>
+              <c:idx val="24"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="2.8623819175895532E-3"/>
-                  <c:y val="1.5264261628002011E-3"/>
+                  <c:x val="0"/>
+                  <c:y val="5.3013283375618085E-3"/>
                 </c:manualLayout>
               </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln w="25400">
-                  <a:noFill/>
-                </a:ln>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans"/>
-                      <a:ea typeface="Noto Sans"/>
-                      <a:cs typeface="Noto Sans"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -979,7 +791,91 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-721E-459A-8DE9-A55E5DF6330D}"/>
+                  <c16:uniqueId val="{00000008-FE66-4E25-B0A0-E0B5B3E3692F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="25"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="6.800793668685504E-4"/>
+                  <c:y val="-1.0602656675123811E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-FE66-4E25-B0A0-E0B5B3E3692F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="35"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="5.3013283375618085E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-FE66-4E25-B0A0-E0B5B3E3692F}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="44"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.0804762012116511E-3"/>
+                  <c:y val="-6.4793264517324391E-17"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-A430-4475-8715-BC0EAEF83F89}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="45"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="6.800793668685504E-4"/>
+                  <c:y val="8.8355472292697881E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-A430-4475-8715-BC0EAEF83F89}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -990,22 +886,17 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Noto Sans"/>
-                    <a:ea typeface="Noto Sans"/>
-                    <a:cs typeface="Noto Sans"/>
+                  <a:defRPr b="1">
+                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="es-MX"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1023,9 +914,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>IED_FBKF_Trimestral!$A$8:$B$115</c:f>
+              <c:f>IED_FBCF_Trimestral!$A$8:$B$117</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="108"/>
+                <c:ptCount val="110"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>I</c:v>
@@ -1350,6 +1241,12 @@
                   </c:pt>
                   <c:pt idx="107">
                     <c:v>IV</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>I</c:v>
+                  </c:pt>
+                  <c:pt idx="109">
+                    <c:v>II</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
@@ -1433,6 +1330,9 @@
                   </c:pt>
                   <c:pt idx="104">
                     <c:v>2025</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>2026</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1440,10 +1340,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IED_FBKF_Trimestral!$E$8:$E$115</c:f>
+              <c:f>IED_FBCF_Trimestral!$E$8:$E$117</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.0</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>11.847175756057394</c:v>
                 </c:pt>
@@ -1529,251 +1429,257 @@
                   <c:v>12.731443378753227</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.0">
-                  <c:v>14.374471040011613</c:v>
+                  <c:v>14.374471040011757</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.0">
-                  <c:v>12.679587484233497</c:v>
+                  <c:v>12.679587484233407</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="0.0">
-                  <c:v>4.1400490552272409</c:v>
+                  <c:v>4.140049055227168</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="0.0">
-                  <c:v>7.986666254798064</c:v>
+                  <c:v>7.9866740198249104</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="0.0">
-                  <c:v>19.343937741275582</c:v>
+                  <c:v>19.343937741275496</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="0.0">
-                  <c:v>10.591263341399403</c:v>
+                  <c:v>10.591263341399305</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="0.0">
-                  <c:v>12.098827491233962</c:v>
+                  <c:v>12.098831109188414</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="0.0">
-                  <c:v>11.220385798717297</c:v>
+                  <c:v>11.220385798717224</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="0.0">
-                  <c:v>13.258590920929834</c:v>
+                  <c:v>13.258590920929759</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="0.0">
-                  <c:v>11.537751587536345</c:v>
+                  <c:v>11.538863054445251</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="0.0">
-                  <c:v>7.5883564859153836</c:v>
+                  <c:v>7.5883564859152877</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="0.0">
-                  <c:v>10.997487883281694</c:v>
+                  <c:v>10.997494102195084</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="0.0">
-                  <c:v>12.678025099737306</c:v>
+                  <c:v>12.678025099737223</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="0.0">
-                  <c:v>11.735470810961804</c:v>
+                  <c:v>11.735470810961694</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="0.0">
-                  <c:v>4.386602606419812</c:v>
+                  <c:v>4.3866031995614314</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="0.0">
-                  <c:v>5.3509155788169789</c:v>
+                  <c:v>5.3509155788169327</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="0.0">
-                  <c:v>15.176045551534067</c:v>
+                  <c:v>15.17604555153409</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="0.0">
-                  <c:v>15.341079647104333</c:v>
+                  <c:v>15.341079647104358</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="0.0">
-                  <c:v>6.4599779187667838</c:v>
+                  <c:v>6.4599779187667528</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="0.0">
-                  <c:v>7.4210515035453968</c:v>
+                  <c:v>7.4210526481475938</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="0.0">
-                  <c:v>13.015612128980758</c:v>
+                  <c:v>13.015618836246739</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="0.0">
-                  <c:v>9.4743383567762507</c:v>
+                  <c:v>9.4743442633309023</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="0.0">
-                  <c:v>5.8884892838582896</c:v>
+                  <c:v>5.8884951338083287</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="0.0">
-                  <c:v>7.8869120081689514</c:v>
+                  <c:v>7.8869132333784604</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="0.0">
-                  <c:v>11.209931325471679</c:v>
+                  <c:v>11.210635050178276</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="0.0">
-                  <c:v>7.9779659771899905</c:v>
+                  <c:v>7.9779659813618879</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="0.0">
-                  <c:v>7.6069497770118497</c:v>
+                  <c:v>7.6073503918356353</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="0.0">
-                  <c:v>3.1010683039473417</c:v>
+                  <c:v>3.1010683017346179</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="0.0">
-                  <c:v>15.078594941725907</c:v>
+                  <c:v>15.078594916230461</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="0.0">
-                  <c:v>28.9893993519864</c:v>
+                  <c:v>28.989399311932019</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="0.0">
-                  <c:v>5.8385847095250023</c:v>
+                  <c:v>5.8390660937443197</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="0.0">
-                  <c:v>16.200225767361925</c:v>
+                  <c:v>16.200230758669552</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="0.0">
-                  <c:v>20.350685695720163</c:v>
+                  <c:v>20.350696846854159</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="0.0">
-                  <c:v>7.6193916312277015</c:v>
+                  <c:v>7.6206483829047791</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="0.0">
-                  <c:v>4.3305474323776636</c:v>
+                  <c:v>4.3305474290500401</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="0.0">
-                  <c:v>9.675297211840423</c:v>
+                  <c:v>9.6752980169337004</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="0.0">
-                  <c:v>18.224737932047109</c:v>
+                  <c:v>18.224737812697605</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="0.0">
-                  <c:v>9.6590525426074691</c:v>
+                  <c:v>9.6590523460425786</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="0.0">
-                  <c:v>13.550353401836848</c:v>
+                  <c:v>13.550746350678446</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="0.0">
-                  <c:v>10.209729410458911</c:v>
+                  <c:v>10.209940871263003</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="0.0">
-                  <c:v>20.898036668074923</c:v>
+                  <c:v>20.898076055947094</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="0.0">
-                  <c:v>9.5119199580401883</c:v>
+                  <c:v>9.5119588438031659</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="0.0">
-                  <c:v>6.5251857966605984</c:v>
+                  <c:v>6.525188441314107</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="0.0">
-                  <c:v>11.171673813414602</c:v>
+                  <c:v>11.171673170562871</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="0.0">
-                  <c:v>21.984664930048869</c:v>
+                  <c:v>22.010108522803328</c:v>
                 </c:pt>
                 <c:pt idx="73" formatCode="0.0">
-                  <c:v>10.158513352358046</c:v>
+                  <c:v>10.15936283609763</c:v>
                 </c:pt>
                 <c:pt idx="74" formatCode="0.0">
-                  <c:v>8.7311365388911675</c:v>
+                  <c:v>8.7396674254171103</c:v>
                 </c:pt>
                 <c:pt idx="75" formatCode="0.0">
-                  <c:v>9.476124589399646</c:v>
+                  <c:v>9.4761328022211266</c:v>
                 </c:pt>
                 <c:pt idx="76" formatCode="0.0">
-                  <c:v>20.275573881894985</c:v>
+                  <c:v>20.275637804156577</c:v>
                 </c:pt>
                 <c:pt idx="77" formatCode="0.0">
-                  <c:v>13.34254740720467</c:v>
+                  <c:v>13.342572534187516</c:v>
                 </c:pt>
                 <c:pt idx="78" formatCode="0.0">
-                  <c:v>5.5705292859707445</c:v>
+                  <c:v>5.5705451769087677</c:v>
                 </c:pt>
                 <c:pt idx="79" formatCode="0.0">
-                  <c:v>8.5246424824283373</c:v>
+                  <c:v>8.528890256381791</c:v>
                 </c:pt>
                 <c:pt idx="80" formatCode="0.0">
-                  <c:v>21.706058241758871</c:v>
+                  <c:v>21.705980539600798</c:v>
                 </c:pt>
                 <c:pt idx="81" formatCode="0.0">
-                  <c:v>9.3389593101471053</c:v>
+                  <c:v>9.5915362555444421</c:v>
                 </c:pt>
                 <c:pt idx="82" formatCode="0.0">
-                  <c:v>11.721413306109028</c:v>
+                  <c:v>11.721464307329473</c:v>
                 </c:pt>
                 <c:pt idx="83" formatCode="0.0">
-                  <c:v>6.4308391308115995</c:v>
+                  <c:v>6.4346406249174111</c:v>
                 </c:pt>
                 <c:pt idx="84" formatCode="0.0">
-                  <c:v>26.329279506893176</c:v>
+                  <c:v>26.331456003831821</c:v>
                 </c:pt>
                 <c:pt idx="85" formatCode="0.0">
-                  <c:v>16.881906534344285</c:v>
+                  <c:v>17.031790814421736</c:v>
                 </c:pt>
                 <c:pt idx="86" formatCode="0.0">
-                  <c:v>2.4235980275685707</c:v>
+                  <c:v>2.426421121174251</c:v>
                 </c:pt>
                 <c:pt idx="87" formatCode="0.0">
-                  <c:v>4.2743623159262851</c:v>
+                  <c:v>4.2765016724988216</c:v>
                 </c:pt>
                 <c:pt idx="88" formatCode="0.0">
-                  <c:v>25.490114592972624</c:v>
+                  <c:v>25.48859759274259</c:v>
                 </c:pt>
                 <c:pt idx="89" formatCode="0.0">
-                  <c:v>8.6187845952459501</c:v>
+                  <c:v>8.6183858976330487</c:v>
                 </c:pt>
                 <c:pt idx="90" formatCode="0.0">
-                  <c:v>8.9216335098187329</c:v>
+                  <c:v>8.9316578610416002</c:v>
                 </c:pt>
                 <c:pt idx="91" formatCode="0.0">
-                  <c:v>6.6706259582065481</c:v>
+                  <c:v>6.6723191598835259</c:v>
                 </c:pt>
                 <c:pt idx="92" formatCode="0.0">
-                  <c:v>30.021393633104097</c:v>
+                  <c:v>30.026947946089017</c:v>
                 </c:pt>
                 <c:pt idx="93" formatCode="0.0">
-                  <c:v>10.271490383536811</c:v>
+                  <c:v>10.273028995833632</c:v>
                 </c:pt>
                 <c:pt idx="94" formatCode="0.0">
-                  <c:v>4.203215659393738</c:v>
+                  <c:v>4.2043825872845231</c:v>
                 </c:pt>
                 <c:pt idx="95" formatCode="0.0">
-                  <c:v>2.0030948057511115</c:v>
+                  <c:v>2.0025534817201462</c:v>
                 </c:pt>
                 <c:pt idx="96" formatCode="0.0">
-                  <c:v>25.29712710186595</c:v>
+                  <c:v>25.27918907055</c:v>
                 </c:pt>
                 <c:pt idx="97" formatCode="0.0">
-                  <c:v>8.4567120641968323</c:v>
+                  <c:v>8.4507884127781523</c:v>
                 </c:pt>
                 <c:pt idx="98" formatCode="0.0">
-                  <c:v>2.6867467753331145</c:v>
+                  <c:v>2.6864508934018021</c:v>
                 </c:pt>
                 <c:pt idx="99" formatCode="0.0">
-                  <c:v>1.0978260556809953</c:v>
+                  <c:v>1.1244300240630904</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="0.0">
-                  <c:v>24.897700766725176</c:v>
+                  <c:v>24.81144434236565</c:v>
                 </c:pt>
                 <c:pt idx="101" formatCode="0.0">
-                  <c:v>5.7230960815176664</c:v>
+                  <c:v>5.7074810888776559</c:v>
                 </c:pt>
                 <c:pt idx="102" formatCode="0.0">
-                  <c:v>2.8538689350131845</c:v>
+                  <c:v>2.8491265392909289</c:v>
                 </c:pt>
                 <c:pt idx="103" formatCode="0.0">
-                  <c:v>1.1131066892617674</c:v>
+                  <c:v>1.1168243951058521</c:v>
                 </c:pt>
                 <c:pt idx="104" formatCode="0.0">
-                  <c:v>25.772815317990084</c:v>
+                  <c:v>25.289621743379282</c:v>
                 </c:pt>
                 <c:pt idx="105" formatCode="0.0">
-                  <c:v>13.705804613380627</c:v>
+                  <c:v>13.855591273380142</c:v>
                 </c:pt>
                 <c:pt idx="106" formatCode="0.0">
-                  <c:v>7.4605683898984729</c:v>
+                  <c:v>7.5722818377320618</c:v>
                 </c:pt>
                 <c:pt idx="107" formatCode="0.0">
-                  <c:v>-4.4283120683521338</c:v>
+                  <c:v>-3.4983284745214354</c:v>
+                </c:pt>
+                <c:pt idx="108" formatCode="0.0">
+                  <c:v>26.481172378566619</c:v>
+                </c:pt>
+                <c:pt idx="109" formatCode="0.0">
+                  <c:v>5.6047015107532108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-721E-459A-8DE9-A55E5DF6330D}"/>
+              <c16:uniqueId val="{00000003-A430-4475-8715-BC0EAEF83F89}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1786,11 +1692,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="90"/>
-        <c:axId val="1791912720"/>
+        <c:axId val="1896861647"/>
         <c:axId val="1"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1791912720"/>
+        <c:axId val="1896861647"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1812,16 +1718,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans"/>
-                <a:ea typeface="Noto Sans"/>
-                <a:cs typeface="Noto Sans"/>
+              <a:defRPr>
+                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-MX"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1"/>
@@ -1859,7 +1762,7 @@
             <a:endParaRPr lang="es-MX"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1791912720"/>
+        <c:crossAx val="1896861647"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1908,7 +1811,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1963,22 +1866,17 @@
               </a:ln>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Noto Sans"/>
-                    <a:ea typeface="Noto Sans"/>
-                    <a:cs typeface="Noto Sans"/>
+                  <a:defRPr b="1">
+                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="es-MX"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1996,7 +1894,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>IED_FBKF_Anual!$A$8:$A$34</c:f>
+              <c:f>IED_FBCF_Anual!$A$8:$A$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="27"/>
@@ -2086,7 +1984,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IED_FBKF_Anual!$D$8:$D$34</c:f>
+              <c:f>IED_FBCF_Anual!$D$8:$D$34</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.0</c:formatCode>
                 <c:ptCount val="27"/>
@@ -2112,71 +2010,71 @@
                   <c:v>13.553538920167924</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.6061841030337867</c:v>
+                  <c:v>9.6061862218891569</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>13.139527590583441</c:v>
+                  <c:v>13.139528515882972</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.74827345540073</c:v>
+                  <c:v>10.74856868605141</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.281437480149263</c:v>
+                  <c:v>8.2814376305751551</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>10.895219858086845</c:v>
+                  <c:v>10.89522018136903</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.9197911087737953</c:v>
+                  <c:v>8.9197959102243569</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.3176164336708425</c:v>
+                  <c:v>7.3178845327725464</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>16.566985174108101</c:v>
+                  <c:v>16.567104529023787</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.28479277636791</c:v>
+                  <c:v>10.285101772469922</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12.826580323931047</c:v>
+                  <c:v>12.826735544757085</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.855839933309531</c:v>
+                  <c:v>11.855859065231295</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>12.272670313794436</c:v>
+                  <c:v>12.280870092893158</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>11.779169253848675</c:v>
+                  <c:v>11.780278666477106</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>12.247429854079341</c:v>
+                  <c:v>12.310675613955063</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>12.410797812354843</c:v>
+                  <c:v>12.441128613242649</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>12.074041427990764</c:v>
+                  <c:v>12.076898695835391</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>11.057670421636736</c:v>
+                  <c:v>11.057987437022518</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8.7055516554481969</c:v>
+                  <c:v>8.7089939940832561</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8.7136287386989171</c:v>
+                  <c:v>8.6801903653949744</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>9.9159608665907353</c:v>
+                  <c:v>10.122966043932729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E56A-4D43-A165-AE2920561AB5}"/>
+              <c16:uniqueId val="{00000000-D552-4A71-8ED4-B7B7C962C671}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2189,11 +2087,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="90"/>
-        <c:axId val="1791909360"/>
+        <c:axId val="1895393839"/>
         <c:axId val="1"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1791909360"/>
+        <c:axId val="1895393839"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2215,16 +2113,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans"/>
-                <a:ea typeface="Noto Sans"/>
-                <a:cs typeface="Noto Sans"/>
+              <a:defRPr>
+                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-MX"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1"/>
@@ -2257,19 +2152,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans"/>
-                <a:ea typeface="Noto Sans"/>
-                <a:cs typeface="Noto Sans"/>
+              <a:defRPr>
+                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-MX"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1791909360"/>
+        <c:crossAx val="1895393839"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2320,22 +2212,22 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
+      <xdr:colOff>230186</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>86518</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>254</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>16383</xdr:col>
+      <xdr:colOff>3100915</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>169334</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1067" name="Gráfico 1">
+        <xdr:cNvPr id="1069" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2386263-70B8-0284-8EA7-448ED95C21D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D040000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2357,23 +2249,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>444520</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
+      <xdr:col>16383</xdr:col>
+      <xdr:colOff>488970</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1068" name="Imagen 4">
+        <xdr:cNvPr id="5" name="Imagen 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04A83A99-89E3-B632-9551-8DDE4F7F23C1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2382,7 +2274,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2396,8 +2288,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="16106775" y="0"/>
-          <a:ext cx="3171825" cy="676275"/>
+          <a:off x="18462645" y="0"/>
+          <a:ext cx="3013075" cy="676275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2431,23 +2323,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
+      <xdr:col>16383</xdr:col>
+      <xdr:colOff>63504</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>16383</xdr:col>
+      <xdr:colOff>3071828</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>209550</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1069" name="Imagen 5">
+        <xdr:cNvPr id="8" name="Imagen 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D626BDF-F7D7-AC92-AF82-073C9F3A0BBD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2470,8 +2362,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="18821400" y="47625"/>
-          <a:ext cx="3209925" cy="638175"/>
+          <a:off x="21050254" y="47625"/>
+          <a:ext cx="3008324" cy="638175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2511,11 +2403,11 @@
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
       <cdr:x>0.00104</cdr:x>
-      <cdr:y>0.09183</cdr:y>
+      <cdr:y>0.08715</cdr:y>
     </cdr:from>
     <cdr:to>
       <cdr:x>0.9813</cdr:x>
-      <cdr:y>0.21715</cdr:y>
+      <cdr:y>0.2137</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -2550,7 +2442,7 @@
               <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t> LA FBKF TRIMESTRAL</a:t>
+            <a:t> LA FBCF TRIMESTRAL ANUALIZADO</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="es-MX" sz="1800" b="1">
@@ -2558,7 +2450,7 @@
               <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>, 1999 - 2025</a:t>
+            <a:t>, 1999 - 2026</a:t>
           </a:r>
         </a:p>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -2582,11 +2474,11 @@
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
       <cdr:x>0.01211</cdr:x>
-      <cdr:y>0.94511</cdr:y>
+      <cdr:y>0.94659</cdr:y>
     </cdr:from>
     <cdr:to>
       <cdr:x>0.47026</cdr:x>
-      <cdr:y>0.98686</cdr:y>
+      <cdr:y>0.98711</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -2626,22 +2518,22 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
+      <xdr:colOff>410076</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>95082</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>250657</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2091" name="Gráfico 2">
+        <xdr:cNvPr id="2093" name="Gráfico 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FCE8DFD-ECBD-425B-AE63-A5F4F03EA66F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002D080000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2670,16 +2562,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
+      <xdr:colOff>639512</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:rowOff>227430</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2092" name="Imagen 4">
+        <xdr:cNvPr id="5" name="Imagen 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5627126-FD01-6DC8-2D03-F7D7EDCA9352}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2688,7 +2580,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2702,8 +2594,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11096625" y="0"/>
-          <a:ext cx="3019425" cy="704850"/>
+          <a:off x="11108531" y="0"/>
+          <a:ext cx="3020762" cy="703680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2738,22 +2630,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>110875</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>23813</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>695325</xdr:colOff>
+      <xdr:colOff>690563</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>217321</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2093" name="Imagen 5">
+        <xdr:cNvPr id="8" name="Imagen 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71CB52F9-F222-633E-9070-C79C80E3BCB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2776,8 +2668,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13592175" y="28575"/>
-          <a:ext cx="3181350" cy="666750"/>
+          <a:off x="13600656" y="23813"/>
+          <a:ext cx="3175251" cy="669758"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2817,11 +2709,11 @@
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
       <cdr:x>0.00528</cdr:x>
-      <cdr:y>0.0256</cdr:y>
+      <cdr:y>0.02536</cdr:y>
     </cdr:from>
     <cdr:to>
       <cdr:x>1</cdr:x>
-      <cdr:y>0.15288</cdr:y>
+      <cdr:y>0.15093</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -2856,7 +2748,7 @@
               <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t> LA FBKF ANUAL</a:t>
+            <a:t> LA FBCF ANUAL</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="es-MX" sz="1300" b="1">
@@ -2884,12 +2776,12 @@
   </cdr:relSizeAnchor>
   <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
     <cdr:from>
-      <cdr:x>0.006</cdr:x>
-      <cdr:y>0.93421</cdr:y>
+      <cdr:x>0.01069</cdr:x>
+      <cdr:y>0.9231</cdr:y>
     </cdr:from>
     <cdr:to>
-      <cdr:x>0.006</cdr:x>
-      <cdr:y>0.93445</cdr:y>
+      <cdr:x>0.46809</cdr:x>
+      <cdr:y>0.99976</cdr:y>
     </cdr:to>
     <cdr:sp macro="" textlink="">
       <cdr:nvSpPr>
@@ -2931,20 +2823,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>428625</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3100" name="Imagen 2">
+        <xdr:cNvPr id="2" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBB73B9C-867D-256A-2DFB-FE37B645C0BD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2953,7 +2845,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2967,7 +2859,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="104775" y="161925"/>
+          <a:off x="104775" y="152400"/>
           <a:ext cx="6419850" cy="9429750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3265,67 +3157,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96B281AB-5041-4EB0-B6C7-6726F0FA4DA1}">
-  <dimension ref="A1:IT121"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:XFC121"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="19.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="3" customWidth="1"/>
-    <col min="7" max="26" width="11.42578125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="12" style="3" customWidth="1"/>
-    <col min="28" max="254" width="11.42578125" style="3" hidden="1" customWidth="1"/>
-    <col min="255" max="255" width="11.42578125" style="3" customWidth="1"/>
-    <col min="256" max="16384" width="5.42578125" style="3"/>
+    <col min="2" max="2" width="14.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.125" style="3" customWidth="1"/>
+    <col min="7" max="26" width="11.375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="1.25" style="3" customWidth="1"/>
+    <col min="28" max="16383" width="11.375" style="3" hidden="1"/>
+    <col min="16384" max="16384" width="52.25" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="62" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:5" s="67" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="67" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:5" s="67" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="70" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="62" customFormat="1" ht="18.75" customHeight="1"/>
-    <row r="3" spans="1:5" s="62" customFormat="1" ht="18.75" customHeight="1"/>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" s="5" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A6" s="65" t="s">
+      <c r="B6" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="65" t="s">
+      <c r="C6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:5" s="5" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="69"/>
+      <c r="E7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="5" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A7" s="66"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="63" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="72">
+        <v>1999</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>6</v>
-      </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="68">
-        <v>1999</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="C8" s="7">
         <v>3596.0751519900109</v>
@@ -3337,10 +3228,10 @@
         <v>11.847175756057394</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="68"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="72"/>
       <c r="B9" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="10">
         <v>3395.8904113800213</v>
@@ -3352,10 +3243,10 @@
         <v>11.105868753376479</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="68"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="72"/>
       <c r="B10" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="10">
         <v>3028.4476429900201</v>
@@ -3367,10 +3258,10 @@
         <v>8.8040005744072314</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="68"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="72"/>
       <c r="B11" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" s="13">
         <v>3939.9046280600205</v>
@@ -3382,12 +3273,12 @@
         <v>10.703827707171227</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="68">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="72">
         <v>2000</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="7">
         <v>4600.6358357300305</v>
@@ -3399,10 +3290,10 @@
         <v>12.38671048306929</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="68"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="72"/>
       <c r="B13" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="10">
         <v>4857.4234801700522</v>
@@ -3414,10 +3305,10 @@
         <v>13.314433691460881</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="68"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="72"/>
       <c r="B14" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="10">
         <v>3056.9462686500078</v>
@@ -3429,10 +3320,10 @@
         <v>7.3151115677930756</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="68"/>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="72"/>
       <c r="B15" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C15" s="13">
         <v>5733.6828056599834</v>
@@ -3444,12 +3335,12 @@
         <v>13.617478456780407</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="68">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="72">
         <v>2001</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" s="7">
         <v>3598.677000336937</v>
@@ -3461,10 +3352,10 @@
         <v>9.5251429099614668</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="68"/>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="72"/>
       <c r="B17" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" s="10">
         <v>5218.8302660300069</v>
@@ -3476,10 +3367,10 @@
         <v>14.102345920828121</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="68"/>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="72"/>
       <c r="B18" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C18" s="10">
         <v>16314.0481983101</v>
@@ -3491,10 +3382,10 @@
         <v>40.025520562136755</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="68"/>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="72"/>
       <c r="B19" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" s="13">
         <v>4925.625658099998</v>
@@ -3506,12 +3397,12 @@
         <v>11.955536595717859</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="68">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="72">
         <v>2002</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" s="7">
         <v>5067.9842793500102</v>
@@ -3523,10 +3414,10 @@
         <v>13.42541367027372</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="68"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="72"/>
       <c r="B21" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C21" s="10">
         <v>6258.5196879300302</v>
@@ -3538,10 +3429,10 @@
         <v>16.509306554667589</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="68"/>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="72"/>
       <c r="B22" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C22" s="10">
         <v>6114.3371770600306</v>
@@ -3553,10 +3444,10 @@
         <v>15.366007047079517</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="68"/>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="72"/>
       <c r="B23" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C23" s="13">
         <v>6658.3650667900283</v>
@@ -3568,12 +3459,12 @@
         <v>16.1455850813363</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="68">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="72">
         <v>2003</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24" s="7">
         <v>3963.6853646000272</v>
@@ -3585,10 +3476,10 @@
         <v>10.566538018503948</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="68"/>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="72"/>
       <c r="B25" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" s="10">
         <v>5547.3362112600416</v>
@@ -3600,10 +3491,10 @@
         <v>14.72589106570245</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="68"/>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="72"/>
       <c r="B26" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26" s="10">
         <v>2521.6765765800192</v>
@@ -3615,10 +3506,10 @@
         <v>6.4724471280715097</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="68"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="72"/>
       <c r="B27" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C27" s="13">
         <v>6217.2706238600022</v>
@@ -3630,12 +3521,12 @@
         <v>15.67079032002443</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="68">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="72">
         <v>2004</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C28" s="7">
         <v>9363.4579323199778</v>
@@ -3647,10 +3538,10 @@
         <v>23.031794337360687</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="68"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="72"/>
       <c r="B29" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29" s="10">
         <v>4351.4961818657594</v>
@@ -3662,10 +3553,10 @@
         <v>10.641166971724095</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="68"/>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="72"/>
       <c r="B30" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C30" s="10">
         <v>3284.9130503884412</v>
@@ -3677,10 +3568,10 @@
         <v>7.748289792997487</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="68"/>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="72"/>
       <c r="B31" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C31" s="13">
         <v>8015.7027005200134</v>
@@ -3692,12 +3583,12 @@
         <v>17.308049020571858</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="68">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="72">
         <v>2005</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C32" s="7">
         <v>6761.6208839399878</v>
@@ -3709,10 +3600,10 @@
         <v>15.464849802694339</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="68"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="72"/>
       <c r="B33" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33" s="10">
         <v>6773.6153674899961</v>
@@ -3724,10 +3615,10 @@
         <v>14.836581381264994</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="68"/>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="72"/>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C34" s="10">
         <v>5478.9247877962507</v>
@@ -3739,10 +3630,10 @@
         <v>11.490792843145215</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="68"/>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="72"/>
       <c r="B35" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C35" s="13">
         <v>6781.6637614100327</v>
@@ -3754,1404 +3645,1344 @@
         <v>12.731443378753227</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="67">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="58">
         <v>2006</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C36" s="19">
-        <v>7437.8564357716077</v>
+        <v>7437.8564357716823</v>
       </c>
       <c r="D36" s="32">
         <v>51743.514005268044</v>
       </c>
       <c r="E36" s="20">
-        <f>C36/D36*100</f>
-        <v>14.374471040011613</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="67"/>
+        <v>14.374471040011757</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="58"/>
       <c r="B37" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C37" s="22">
-        <v>6634.3109912895179</v>
+        <v>6634.3109912894688</v>
       </c>
       <c r="D37" s="34">
         <v>52322.766805615618</v>
       </c>
       <c r="E37" s="23">
-        <f t="shared" ref="E37:E100" si="0">C37/D37*100</f>
-        <v>12.679587484233497</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="67"/>
+        <v>12.679587484233407</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="58"/>
       <c r="B38" s="21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C38" s="22">
-        <v>2346.7229354590299</v>
+        <v>2346.7229354589886</v>
       </c>
       <c r="D38" s="34">
         <v>56683.457228509142</v>
       </c>
       <c r="E38" s="23">
-        <f t="shared" si="0"/>
-        <v>4.1400490552272409</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="67"/>
+        <v>4.140049055227168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="58"/>
       <c r="B39" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C39" s="25">
-        <v>4817.9585849310697</v>
+        <v>4817.9632691856214</v>
       </c>
       <c r="D39" s="36">
         <v>60325.027129268565</v>
       </c>
       <c r="E39" s="26">
-        <f t="shared" si="0"/>
-        <v>7.986666254798064</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="67">
+        <v>7.9866740198249104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="58">
         <v>2007</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C40" s="19">
-        <v>10815.781410870057</v>
+        <v>10815.781410870009</v>
       </c>
       <c r="D40" s="32">
         <v>55913.02844090337</v>
       </c>
       <c r="E40" s="20">
-        <f t="shared" si="0"/>
-        <v>19.343937741275582</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="67"/>
+        <v>19.343937741275496</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="58"/>
       <c r="B41" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C41" s="22">
-        <v>6137.6383039077155</v>
+        <v>6137.6383039076591</v>
       </c>
       <c r="D41" s="34">
         <v>57950.011307119115</v>
       </c>
       <c r="E41" s="23">
-        <f t="shared" si="0"/>
-        <v>10.591263341399403</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="67"/>
+        <v>10.591263341399305</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="58"/>
       <c r="B42" s="21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C42" s="22">
-        <v>7628.6535878138066</v>
+        <v>7628.6558690366146</v>
       </c>
       <c r="D42" s="34">
         <v>63052.833783612856</v>
       </c>
       <c r="E42" s="23">
-        <f t="shared" si="0"/>
-        <v>12.098827491233962</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="67"/>
+        <v>12.098831109188414</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="58"/>
       <c r="B43" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C43" s="25">
-        <v>7811.9645158699423</v>
+        <v>7811.9645158698904</v>
       </c>
       <c r="D43" s="36">
         <v>69622.958212034006</v>
       </c>
       <c r="E43" s="26">
-        <f t="shared" si="0"/>
-        <v>11.220385798717297</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="67">
+        <v>11.220385798717224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="58">
         <v>2008</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C44" s="19">
-        <v>8554.8315152352734</v>
+        <v>8554.8315152352243</v>
       </c>
       <c r="D44" s="32">
         <v>64522.931329985688</v>
       </c>
       <c r="E44" s="20">
-        <f t="shared" si="0"/>
-        <v>13.258590920929834</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="67"/>
+        <v>13.258590920929759</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="58"/>
       <c r="B45" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C45" s="22">
-        <v>8376.7569183731575</v>
+        <v>8377.5638769948691</v>
       </c>
       <c r="D45" s="34">
         <v>72603.027156713521</v>
       </c>
       <c r="E45" s="23">
-        <f t="shared" si="0"/>
-        <v>11.537751587536345</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="67"/>
+        <v>11.538863054445251</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="58"/>
       <c r="B46" s="21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C46" s="22">
-        <v>5644.1373640638449</v>
+        <v>5644.1373640637739</v>
       </c>
       <c r="D46" s="34">
         <v>74378.916891158588</v>
       </c>
       <c r="E46" s="23">
-        <f t="shared" si="0"/>
-        <v>7.5883564859153836</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="67"/>
+        <v>7.5883564859152877</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="58"/>
       <c r="B47" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C47" s="25">
-        <v>6945.6932731704892</v>
+        <v>6945.6972008551884</v>
       </c>
       <c r="D47" s="36">
         <v>63157.089572513047</v>
       </c>
       <c r="E47" s="26">
-        <f t="shared" si="0"/>
-        <v>10.997487883281694</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="67">
+        <v>10.997494102195084</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="58">
         <v>2009</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C48" s="19">
-        <v>6105.2954136300341</v>
+        <v>6105.2954136299941</v>
       </c>
       <c r="D48" s="32">
         <v>48156.517798316541</v>
       </c>
       <c r="E48" s="20">
-        <f t="shared" si="0"/>
-        <v>12.678025099737306</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="67"/>
+        <v>12.678025099737223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="58"/>
       <c r="B49" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C49" s="22">
-        <v>6094.493354614352</v>
+        <v>6094.4933546142947</v>
       </c>
       <c r="D49" s="34">
         <v>51932.244157785652</v>
       </c>
       <c r="E49" s="23">
-        <f t="shared" si="0"/>
-        <v>11.735470810961804</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="67"/>
+        <v>11.735470810961694</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="58"/>
       <c r="B50" s="21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C50" s="22">
-        <v>2398.0365921942885</v>
+        <v>2398.0369164487138</v>
       </c>
       <c r="D50" s="34">
         <v>54667.285992233519</v>
       </c>
       <c r="E50" s="23">
-        <f t="shared" si="0"/>
-        <v>4.386602606419812</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="67"/>
+        <v>4.3866031995614314</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="58"/>
       <c r="B51" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C51" s="25">
-        <v>3253.4346149189305</v>
+        <v>3253.4346149189023</v>
       </c>
       <c r="D51" s="36">
         <v>60801.456629189139</v>
       </c>
       <c r="E51" s="26">
-        <f t="shared" si="0"/>
-        <v>5.3509155788169789</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="67">
+        <v>5.3509155788169327</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="58">
         <v>2010</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C52" s="19">
-        <v>8722.7916987426652</v>
+        <v>8722.7916987426779</v>
       </c>
       <c r="D52" s="32">
         <v>57477.368983390559</v>
       </c>
       <c r="E52" s="20">
-        <f t="shared" si="0"/>
-        <v>15.176045551534067</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="67"/>
+        <v>15.17604555153409</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="58"/>
       <c r="B53" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C53" s="22">
-        <v>9301.6213772700157</v>
+        <v>9301.6213772700303</v>
       </c>
       <c r="D53" s="34">
         <v>60632.117108040176</v>
       </c>
       <c r="E53" s="23">
-        <f t="shared" si="0"/>
-        <v>15.341079647104333</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="67"/>
+        <v>15.341079647104358</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="58"/>
       <c r="B54" s="21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C54" s="22">
-        <v>3942.0841229426032</v>
+        <v>3942.0841229425846</v>
       </c>
       <c r="D54" s="34">
         <v>61023.182625601781</v>
       </c>
       <c r="E54" s="23">
-        <f t="shared" si="0"/>
-        <v>6.4599779187667838</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="67"/>
+        <v>6.4599779187667528</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="58"/>
       <c r="B55" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C55" s="25">
-        <v>5232.5043760000099</v>
+        <v>5232.5051830468292</v>
       </c>
       <c r="D55" s="36">
         <v>70508.934933279859</v>
       </c>
       <c r="E55" s="26">
-        <f t="shared" si="0"/>
-        <v>7.4210515035453968</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="67">
+        <v>7.4210526481475938</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="58">
         <v>2011</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C56" s="19">
-        <v>8431.2191248084346</v>
+        <v>8431.2234696236192</v>
       </c>
       <c r="D56" s="32">
         <v>64777.738006154585</v>
       </c>
       <c r="E56" s="20">
-        <f t="shared" si="0"/>
-        <v>13.015612128980758</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="67"/>
+        <v>13.015618836246739</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="58"/>
       <c r="B57" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C57" s="22">
-        <v>6697.4453847119985</v>
+        <v>6697.4495600776772</v>
       </c>
       <c r="D57" s="34">
         <v>70690.375755071509</v>
       </c>
       <c r="E57" s="23">
-        <f t="shared" si="0"/>
-        <v>9.4743383567762507</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="67"/>
+        <v>9.4743442633309023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="58"/>
       <c r="B58" s="21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C58" s="22">
-        <v>4349.890992388333</v>
+        <v>4349.8953138099669</v>
       </c>
       <c r="D58" s="34">
         <v>73871.086159779385</v>
       </c>
       <c r="E58" s="23">
-        <f t="shared" si="0"/>
-        <v>5.8884892838582896</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="67"/>
+        <v>5.8884951338083287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="58"/>
       <c r="B59" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C59" s="25">
-        <v>6154.0092889798389</v>
+        <v>6154.0102435415483</v>
       </c>
       <c r="D59" s="36">
-        <v>78028.121558929008</v>
+        <v>78028.121540591601</v>
       </c>
       <c r="E59" s="26">
-        <f t="shared" si="0"/>
-        <v>7.8869120081689514</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="67">
+        <v>7.8869132333784604</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="58">
         <v>2012</v>
       </c>
       <c r="B60" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="19">
+        <v>7893.1890991886285</v>
+      </c>
+      <c r="D60" s="32">
+        <v>70408.046144211141</v>
+      </c>
+      <c r="E60" s="20">
+        <v>11.210635050178276</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="58"/>
+      <c r="B61" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="22">
+        <v>5622.1308966418355</v>
+      </c>
+      <c r="D61" s="34">
+        <v>70470.730381355956</v>
+      </c>
+      <c r="E61" s="23">
+        <v>7.9779659813618879</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="58"/>
+      <c r="B62" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C60" s="19">
-        <v>7892.6936246853675</v>
-      </c>
-      <c r="D60" s="32">
-        <v>70408.04618268495</v>
-      </c>
-      <c r="E60" s="20">
-        <f t="shared" si="0"/>
-        <v>11.209931325471679</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="67"/>
-      <c r="B61" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="22">
-        <v>5622.1308966418583</v>
-      </c>
-      <c r="D61" s="34">
-        <v>70470.730418207328</v>
-      </c>
-      <c r="E61" s="23">
-        <f t="shared" si="0"/>
-        <v>7.9779659771899905</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="67"/>
-      <c r="B62" s="21" t="s">
-        <v>10</v>
-      </c>
       <c r="C62" s="22">
-        <v>5736.2922657135723</v>
+        <v>5736.5943636348911</v>
       </c>
       <c r="D62" s="34">
         <v>75408.572869096737</v>
       </c>
       <c r="E62" s="23">
-        <f t="shared" si="0"/>
-        <v>7.6069497770118497</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="67"/>
+        <v>7.6073503918356353</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="58"/>
       <c r="B63" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C63" s="25">
-        <v>2518.2153452201637</v>
+        <v>2518.2153452201601</v>
       </c>
       <c r="D63" s="36">
-        <v>81204.768757100072</v>
+        <v>81204.768815042466</v>
       </c>
       <c r="E63" s="26">
-        <f t="shared" si="0"/>
-        <v>3.1010683039473417</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="67">
+        <v>3.1010683017346179</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="58">
         <v>2013</v>
       </c>
       <c r="B64" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="19">
+        <v>10571.579649062236</v>
+      </c>
+      <c r="D64" s="32">
+        <v>70109.845829753569</v>
+      </c>
+      <c r="E64" s="20">
+        <v>15.078594916230461</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="58"/>
+      <c r="B65" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="22">
+        <v>21019.149824980734</v>
+      </c>
+      <c r="D65" s="34">
+        <v>72506.331017108256</v>
+      </c>
+      <c r="E65" s="23">
+        <v>28.989399311932019</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="58"/>
+      <c r="B66" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C64" s="19">
-        <v>10571.579649062274</v>
-      </c>
-      <c r="D64" s="32">
-        <v>70109.845711209506</v>
-      </c>
-      <c r="E64" s="20">
-        <f t="shared" si="0"/>
-        <v>15.078594941725907</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="67"/>
-      <c r="B65" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" s="22">
-        <v>21019.149824980846</v>
-      </c>
-      <c r="D65" s="34">
-        <v>72506.330916927327</v>
-      </c>
-      <c r="E65" s="23">
-        <f t="shared" si="0"/>
-        <v>28.9893993519864</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="67"/>
-      <c r="B66" s="21" t="s">
-        <v>10</v>
-      </c>
       <c r="C66" s="22">
-        <v>4178.8102629067153</v>
+        <v>4179.1548007384272</v>
       </c>
       <c r="D66" s="34">
         <v>71572.315395021171</v>
       </c>
       <c r="E66" s="23">
-        <f t="shared" si="0"/>
-        <v>5.8385847095250023</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="67"/>
+        <v>5.8390660937443197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="58"/>
       <c r="B67" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C67" s="25">
-        <v>12587.220274832252</v>
+        <v>12587.224112553356</v>
       </c>
       <c r="D67" s="36">
-        <v>77697.807768773942</v>
+        <v>77697.807519299109</v>
       </c>
       <c r="E67" s="26">
-        <f t="shared" si="0"/>
-        <v>16.200225767361925</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="67">
+        <v>16.200230758669552</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="58">
         <v>2014</v>
       </c>
       <c r="B68" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="19">
+        <v>13828.008345434158</v>
+      </c>
+      <c r="D68" s="32">
+        <v>67948.574191314299</v>
+      </c>
+      <c r="E68" s="20">
+        <v>20.350696846854159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="58"/>
+      <c r="B69" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="22">
+        <v>5479.8254865877934</v>
+      </c>
+      <c r="D69" s="34">
+        <v>71907.601705919893</v>
+      </c>
+      <c r="E69" s="23">
+        <v>7.6206483829047791</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="58"/>
+      <c r="B70" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="19">
-        <v>13828.000864523021</v>
-      </c>
-      <c r="D68" s="32">
-        <v>67948.574663659165</v>
-      </c>
-      <c r="E68" s="20">
-        <f t="shared" si="0"/>
-        <v>20.350685695720163</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="67"/>
-      <c r="B69" s="21" t="s">
+      <c r="C70" s="22">
+        <v>3222.1242099690262</v>
+      </c>
+      <c r="D70" s="34">
+        <v>74404.547294747899</v>
+      </c>
+      <c r="E70" s="23">
+        <v>4.3305474290500401</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="62"/>
+      <c r="B71" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C69" s="22">
-        <v>5478.9218144462302</v>
-      </c>
-      <c r="D69" s="34">
-        <v>71907.602071419184</v>
-      </c>
-      <c r="E69" s="23">
-        <f t="shared" si="0"/>
-        <v>7.6193916312277015</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="67"/>
-      <c r="B70" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="22">
-        <v>3222.1242099690189</v>
-      </c>
-      <c r="D70" s="34">
-        <v>74404.547237574749</v>
-      </c>
-      <c r="E70" s="23">
-        <f t="shared" si="0"/>
-        <v>4.3305474323776636</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="69"/>
-      <c r="B71" s="21" t="s">
-        <v>11</v>
-      </c>
       <c r="C71" s="22">
-        <v>7822.4502266866257</v>
+        <v>7822.4509491256849</v>
       </c>
       <c r="D71" s="36">
-        <v>80849.715056956353</v>
+        <v>80849.715796193937</v>
       </c>
       <c r="E71" s="26">
-        <f t="shared" si="0"/>
-        <v>9.675297211840423</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="69">
+        <v>9.6752980169337004</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="62">
         <v>2015</v>
       </c>
       <c r="B72" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="19">
+        <v>12136.456160464986</v>
+      </c>
+      <c r="D72" s="32">
+        <v>66593.310066766673</v>
+      </c>
+      <c r="E72" s="20">
+        <v>18.224737812697605</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="63"/>
+      <c r="B73" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="29">
+        <v>6656.8488480026217</v>
+      </c>
+      <c r="D73" s="34">
+        <v>68918.239693876458</v>
+      </c>
+      <c r="E73" s="23">
+        <v>9.6590523460425786</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="63"/>
+      <c r="B74" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="19">
-        <v>12136.455959530873</v>
-      </c>
-      <c r="D72" s="32">
-        <v>66593.308528127818</v>
-      </c>
-      <c r="E72" s="20">
-        <f t="shared" si="0"/>
-        <v>18.224737932047109</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="70"/>
-      <c r="B73" s="28" t="s">
+      <c r="C74" s="29">
+        <v>9635.9171847840498</v>
+      </c>
+      <c r="D74" s="34">
+        <v>71109.863142716174</v>
+      </c>
+      <c r="E74" s="23">
+        <v>13.550746350678446</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="64"/>
+      <c r="B75" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C73" s="29">
-        <v>6656.8488480026253</v>
-      </c>
-      <c r="D73" s="34">
-        <v>68918.238291367685</v>
-      </c>
-      <c r="E73" s="23">
-        <f t="shared" si="0"/>
-        <v>9.6590525426074691</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="70"/>
-      <c r="B74" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="29">
-        <v>9635.6377676483353</v>
-      </c>
-      <c r="D74" s="34">
-        <v>71109.863203583722</v>
-      </c>
-      <c r="E74" s="23">
-        <f t="shared" si="0"/>
-        <v>13.550353401836848</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="71"/>
-      <c r="B75" s="28" t="s">
-        <v>11</v>
-      </c>
       <c r="C75" s="29">
-        <v>7516.2303818237178</v>
+        <v>7516.3857907193606</v>
       </c>
       <c r="D75" s="36">
-        <v>73618.311315126964</v>
+        <v>73618.308719838446</v>
       </c>
       <c r="E75" s="26">
-        <f t="shared" si="0"/>
-        <v>10.209729410458911</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="72">
+        <v>10.209940871263003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="56">
         <v>2016</v>
       </c>
       <c r="B76" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="19">
+        <v>12805.707928444443</v>
+      </c>
+      <c r="D76" s="32">
+        <v>61276.970636731145</v>
+      </c>
+      <c r="E76" s="20">
+        <v>20.898076055947094</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="65"/>
+      <c r="B77" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="22">
+        <v>6210.7718798170008</v>
+      </c>
+      <c r="D77" s="34">
+        <v>65294.351897487271</v>
+      </c>
+      <c r="E77" s="23">
+        <v>9.5119588438031659</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="65"/>
+      <c r="B78" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C76" s="19">
-        <v>12805.685004525179</v>
-      </c>
-      <c r="D76" s="32">
-        <v>61276.976435245233</v>
-      </c>
-      <c r="E76" s="20">
-        <f t="shared" si="0"/>
-        <v>20.898036668074923</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="73"/>
-      <c r="B77" s="21" t="s">
+      <c r="C78" s="22">
+        <v>4320.1002884910922</v>
+      </c>
+      <c r="D78" s="34">
+        <v>66206.521502711839</v>
+      </c>
+      <c r="E78" s="23">
+        <v>6.525188441314107</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="65"/>
+      <c r="B79" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C77" s="22">
-        <v>6210.7469518721646</v>
-      </c>
-      <c r="D77" s="34">
-        <v>65294.356757306137</v>
-      </c>
-      <c r="E77" s="23">
-        <f t="shared" si="0"/>
-        <v>9.5119199580401883</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="73"/>
-      <c r="B78" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="22">
-        <v>4320.0985201552676</v>
-      </c>
-      <c r="D78" s="34">
-        <v>66206.521236010914</v>
-      </c>
-      <c r="E78" s="23">
-        <f t="shared" si="0"/>
-        <v>6.5251857966605984</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="73"/>
-      <c r="B79" s="21" t="s">
-        <v>11</v>
-      </c>
       <c r="C79" s="22">
-        <v>7855.7742798719855</v>
+        <v>7855.7748850580883</v>
       </c>
       <c r="D79" s="36">
-        <v>70318.686448211665</v>
+        <v>70318.69591170903</v>
       </c>
       <c r="E79" s="26">
-        <f t="shared" si="0"/>
-        <v>11.171673813414602</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="69">
+        <v>11.171673170562871</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="62">
         <v>2017</v>
       </c>
       <c r="B80" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="19">
+        <v>13796.267995389069</v>
+      </c>
+      <c r="D80" s="32">
+        <v>62681.508276506676</v>
+      </c>
+      <c r="E80" s="20">
+        <v>22.010108522803328</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="63"/>
+      <c r="B81" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="22">
+        <v>6837.9154540115687</v>
+      </c>
+      <c r="D81" s="34">
+        <v>67306.538454513153</v>
+      </c>
+      <c r="E81" s="23">
+        <v>10.15936283609763</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="63"/>
+      <c r="B82" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C80" s="19">
-        <v>13780.315352408652</v>
-      </c>
-      <c r="D80" s="32">
-        <v>62681.48910276805</v>
-      </c>
-      <c r="E80" s="20">
-        <f t="shared" si="0"/>
-        <v>21.984664930048869</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="70"/>
-      <c r="B81" s="21" t="s">
+      <c r="C82" s="22">
+        <v>6367.7167730897245</v>
+      </c>
+      <c r="D82" s="34">
+        <v>72859.943784254676</v>
+      </c>
+      <c r="E82" s="23">
+        <v>8.7396674254171103</v>
+      </c>
+      <c r="F82" s="3"/>
+    </row>
+    <row r="83" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="63"/>
+      <c r="B83" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C81" s="22">
-        <v>6837.3419401765786</v>
-      </c>
-      <c r="D81" s="34">
-        <v>67306.521171126486</v>
-      </c>
-      <c r="E81" s="23">
-        <f t="shared" si="0"/>
-        <v>10.158513352358046</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" s="30" customFormat="1">
-      <c r="A82" s="70"/>
-      <c r="B82" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="22">
-        <v>6361.5013980808271</v>
-      </c>
-      <c r="D82" s="34">
-        <v>72859.946351139326</v>
-      </c>
-      <c r="E82" s="23">
-        <f t="shared" si="0"/>
-        <v>8.7311365388911675</v>
-      </c>
-      <c r="F82" s="3"/>
-    </row>
-    <row r="83" spans="1:6" s="30" customFormat="1">
-      <c r="A83" s="70"/>
-      <c r="B83" s="21" t="s">
-        <v>11</v>
-      </c>
       <c r="C83" s="22">
-        <v>7062.6647916455304</v>
+        <v>7062.6675908012876</v>
       </c>
       <c r="D83" s="34">
-        <v>74531.151685638411</v>
+        <v>74531.116629621916</v>
       </c>
       <c r="E83" s="26">
-        <f t="shared" si="0"/>
-        <v>9.476124589399646</v>
+        <v>9.4761328022211266</v>
       </c>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84" s="69">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="62">
         <v>2018</v>
       </c>
       <c r="B84" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="19">
+        <v>14075.4335520269</v>
+      </c>
+      <c r="D84" s="32">
+        <v>69420.423110642601</v>
+      </c>
+      <c r="E84" s="20">
+        <v>20.275637804156577</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="63"/>
+      <c r="B85" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="22">
+        <v>9579.7261917656724</v>
+      </c>
+      <c r="D85" s="34">
+        <v>71798.19459268183</v>
+      </c>
+      <c r="E85" s="23">
+        <v>13.342572534187516</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="63"/>
+      <c r="B86" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C84" s="19">
-        <v>14075.40459729129</v>
-      </c>
-      <c r="D84" s="32">
-        <v>69420.499164563138</v>
-      </c>
-      <c r="E84" s="20">
-        <f t="shared" si="0"/>
-        <v>20.275573881894985</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="70"/>
-      <c r="B85" s="33" t="s">
+      <c r="C86" s="22">
+        <v>4133.5281198081648</v>
+      </c>
+      <c r="D86" s="34">
+        <v>74203.295881031896</v>
+      </c>
+      <c r="E86" s="23">
+        <v>5.5705451769087677</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="64"/>
+      <c r="B87" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C85" s="22">
-        <v>9579.7159451963635</v>
-      </c>
-      <c r="D85" s="34">
-        <v>71798.253008443775</v>
-      </c>
-      <c r="E85" s="23">
-        <f t="shared" si="0"/>
-        <v>13.34254740720467</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" s="70"/>
-      <c r="B86" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="22">
-        <v>4133.5158426340558</v>
-      </c>
-      <c r="D86" s="34">
-        <v>74203.287164187874</v>
-      </c>
-      <c r="E86" s="23">
-        <f t="shared" si="0"/>
-        <v>5.5705292859707445</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" s="71"/>
-      <c r="B87" s="35" t="s">
-        <v>11</v>
-      </c>
       <c r="C87" s="25">
-        <v>6322.2748553898646</v>
+        <v>6325.4355108148338</v>
       </c>
       <c r="D87" s="36">
-        <v>74164.692166525856</v>
+        <v>74164.813014000159</v>
       </c>
       <c r="E87" s="26">
-        <f t="shared" si="0"/>
-        <v>8.5246424824283373</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88" s="69">
+        <v>8.528890256381791</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="62">
         <v>2019</v>
       </c>
       <c r="B88" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="19">
+        <v>15213.119239410031</v>
+      </c>
+      <c r="D88" s="32">
+        <v>70087.224171490117</v>
+      </c>
+      <c r="E88" s="20">
+        <v>21.705980539600798</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="63"/>
+      <c r="B89" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="22">
+        <v>6682.8181742219622</v>
+      </c>
+      <c r="D89" s="34">
+        <v>69674.116806459671</v>
+      </c>
+      <c r="E89" s="23">
+        <v>9.5915362555444421</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="63"/>
+      <c r="B90" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C88" s="19">
-        <v>15213.116431553977</v>
-      </c>
-      <c r="D88" s="32">
-        <v>70086.96034126755</v>
-      </c>
-      <c r="E88" s="20">
-        <f t="shared" si="0"/>
-        <v>21.706058241758871</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89" s="70"/>
-      <c r="B89" s="33" t="s">
+      <c r="C90" s="22">
+        <v>8218.7371136147758</v>
+      </c>
+      <c r="D90" s="34">
+        <v>70116.982811401554</v>
+      </c>
+      <c r="E90" s="23">
+        <v>11.721464307329473</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="64"/>
+      <c r="B91" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C89" s="22">
-        <v>6506.8206192988437</v>
-      </c>
-      <c r="D89" s="34">
-        <v>69673.936926022972</v>
-      </c>
-      <c r="E89" s="23">
-        <f t="shared" si="0"/>
-        <v>9.3389593101471053</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90" s="70"/>
-      <c r="B90" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="22">
-        <v>8218.6973039439381</v>
-      </c>
-      <c r="D90" s="34">
-        <v>70116.9482664729</v>
-      </c>
-      <c r="E90" s="23">
-        <f t="shared" si="0"/>
-        <v>11.721413306109028</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" s="71"/>
-      <c r="B91" s="35" t="s">
-        <v>11</v>
-      </c>
       <c r="C91" s="25">
-        <v>4681.1140034669561</v>
+        <v>4683.8505065180452</v>
       </c>
       <c r="D91" s="36">
-        <v>72791.651419776375</v>
+        <v>72791.174823040914</v>
       </c>
       <c r="E91" s="26">
-        <f t="shared" si="0"/>
-        <v>6.4308391308115995</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="72">
+        <v>6.4346406249174111</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="56">
         <v>2020</v>
       </c>
       <c r="B92" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="19">
+        <v>16783.705275104265</v>
+      </c>
+      <c r="D92" s="32">
+        <v>63740.133749770066</v>
+      </c>
+      <c r="E92" s="20">
+        <v>26.331456003831821</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="65"/>
+      <c r="B93" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="22">
+        <v>7377.6475508395852</v>
+      </c>
+      <c r="D93" s="34">
+        <v>43316.922050219953</v>
+      </c>
+      <c r="E93" s="23">
+        <v>17.031790814421736</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="65"/>
+      <c r="B94" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C92" s="19">
-        <v>16782.618658183317</v>
-      </c>
-      <c r="D92" s="32">
-        <v>63741.275767874766</v>
-      </c>
-      <c r="E92" s="20">
-        <f t="shared" si="0"/>
-        <v>26.329279506893176</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93" s="73"/>
-      <c r="B93" s="21" t="s">
+      <c r="C94" s="22">
+        <v>1339.3389183585498</v>
+      </c>
+      <c r="D94" s="34">
+        <v>55198.12313991008</v>
+      </c>
+      <c r="E94" s="23">
+        <v>2.426421121174251</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="57"/>
+      <c r="B95" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C93" s="22">
-        <v>7312.7951377603413</v>
-      </c>
-      <c r="D93" s="34">
-        <v>43317.353539917458</v>
-      </c>
-      <c r="E93" s="23">
-        <f t="shared" si="0"/>
-        <v>16.881906534344285</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94" s="73"/>
-      <c r="B94" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="22">
-        <v>1337.7820705489009</v>
-      </c>
-      <c r="D94" s="34">
-        <v>55198.182839379748</v>
-      </c>
-      <c r="E94" s="23">
-        <f t="shared" si="0"/>
-        <v>2.4235980275685707</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95" s="74"/>
-      <c r="B95" s="24" t="s">
-        <v>11</v>
-      </c>
       <c r="C95" s="25">
-        <v>2782.0905551690689</v>
+        <v>2783.5542884482593</v>
       </c>
       <c r="D95" s="36">
-        <v>65087.850526919356</v>
+        <v>65089.517124444108</v>
       </c>
       <c r="E95" s="26">
-        <f t="shared" si="0"/>
-        <v>4.2743623159262851</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="72">
+        <v>4.2765016724988216</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="56">
         <v>2021</v>
       </c>
       <c r="B96" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="19">
+        <v>16503.341052883206</v>
+      </c>
+      <c r="D96" s="32">
+        <v>64747.936769899919</v>
+      </c>
+      <c r="E96" s="20">
+        <v>25.48859759274259</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="65"/>
+      <c r="B97" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="22">
+        <v>5927.4276814773821</v>
+      </c>
+      <c r="D97" s="34">
+        <v>68776.540664131651</v>
+      </c>
+      <c r="E97" s="23">
+        <v>8.6183858976330487</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="65"/>
+      <c r="B98" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C96" s="19">
-        <v>16503.338739883602</v>
-      </c>
-      <c r="D96" s="32">
-        <v>64744.074333951452</v>
-      </c>
-      <c r="E96" s="20">
-        <f t="shared" si="0"/>
-        <v>25.490114592972624</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="73"/>
-      <c r="B97" s="28" t="s">
+      <c r="C98" s="22">
+        <v>6439.8444752176238</v>
+      </c>
+      <c r="D98" s="34">
+        <v>72101.334101781365</v>
+      </c>
+      <c r="E98" s="23">
+        <v>8.9316578610416002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="57"/>
+      <c r="B99" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C97" s="22">
-        <v>5927.4183546739514</v>
-      </c>
-      <c r="D97" s="34">
-        <v>68773.250905278066</v>
-      </c>
-      <c r="E97" s="23">
-        <f t="shared" si="0"/>
-        <v>8.6187845952459501</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="73"/>
-      <c r="B98" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C98" s="22">
-        <v>6432.6462084656587</v>
-      </c>
-      <c r="D98" s="34">
-        <v>72101.663909262687</v>
-      </c>
-      <c r="E98" s="23">
-        <f t="shared" si="0"/>
-        <v>8.9216335098187329</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="74"/>
-      <c r="B99" s="21" t="s">
-        <v>11</v>
-      </c>
       <c r="C99" s="25">
-        <v>4983.6119031798971</v>
+        <v>4984.4339488779478</v>
       </c>
       <c r="D99" s="36">
-        <v>74709.808860573277</v>
+        <v>74703.170358609728</v>
       </c>
       <c r="E99" s="26">
-        <f t="shared" si="0"/>
-        <v>6.6706259582065481</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="76">
+        <v>6.6723191598835259</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="59">
         <v>2022</v>
       </c>
       <c r="B100" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="19">
+        <v>22783.259143496824</v>
+      </c>
+      <c r="D100" s="32">
+        <v>75876.040363483975</v>
+      </c>
+      <c r="E100" s="20">
+        <v>30.026947946089017</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="60"/>
+      <c r="B101" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="22">
+        <v>8389.640856693366</v>
+      </c>
+      <c r="D101" s="34">
+        <v>81666.671632056125</v>
+      </c>
+      <c r="E101" s="23">
+        <v>10.273028995833632</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="60"/>
+      <c r="B102" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="19">
-        <v>22783.230884297209</v>
-      </c>
-      <c r="D100" s="32">
-        <v>75889.984198383492</v>
-      </c>
-      <c r="E100" s="20">
-        <f t="shared" si="0"/>
-        <v>30.021393633104097</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="77"/>
-      <c r="B101" s="21" t="s">
+      <c r="C102" s="22">
+        <v>3450.3624601140632</v>
+      </c>
+      <c r="D102" s="34">
+        <v>82065.853629713136</v>
+      </c>
+      <c r="E102" s="23">
+        <v>4.2043825872845231</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="61"/>
+      <c r="B103" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C101" s="22">
-        <v>8389.5554570227341</v>
-      </c>
-      <c r="D101" s="34">
-        <v>81678.073422232366</v>
-      </c>
-      <c r="E101" s="23">
-        <f t="shared" ref="E101:E115" si="1">C101/D101*100</f>
-        <v>10.271490383536811</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="77"/>
-      <c r="B102" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="22">
-        <v>3449.3645464216743</v>
-      </c>
-      <c r="D102" s="34">
-        <v>82064.895687964832</v>
-      </c>
-      <c r="E102" s="23">
-        <f t="shared" si="1"/>
-        <v>4.203215659393738</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A103" s="78"/>
-      <c r="B103" s="24" t="s">
-        <v>11</v>
-      </c>
       <c r="C103" s="25">
-        <v>1797.3013079805078</v>
+        <v>1797.3194814036085</v>
       </c>
       <c r="D103" s="36">
-        <v>89726.222783876845</v>
+        <v>89751.384809945434</v>
       </c>
       <c r="E103" s="26">
-        <f t="shared" si="1"/>
-        <v>2.0030948057511115</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A104" s="72">
+        <v>2.0025534817201462</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="56">
         <v>2023</v>
       </c>
       <c r="B104" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="19">
+        <v>23658.680795907672</v>
+      </c>
+      <c r="D104" s="32">
+        <v>93589.555938207675</v>
+      </c>
+      <c r="E104" s="20">
+        <v>25.27918907055</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="65"/>
+      <c r="B105" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="22">
+        <v>8645.0936630379474</v>
+      </c>
+      <c r="D105" s="34">
+        <v>102299.25588914275</v>
+      </c>
+      <c r="E105" s="23">
+        <v>8.4507884127781523</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="65"/>
+      <c r="B106" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C104" s="19">
-        <v>23658.664414511535</v>
-      </c>
-      <c r="D104" s="32">
-        <v>93523.127425668979</v>
-      </c>
-      <c r="E104" s="20">
-        <f t="shared" si="1"/>
-        <v>25.29712710186595</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A105" s="73"/>
-      <c r="B105" s="21" t="s">
+      <c r="C106" s="22">
+        <v>2911.2510726828878</v>
+      </c>
+      <c r="D106" s="34">
+        <v>108367.92438057282</v>
+      </c>
+      <c r="E106" s="23">
+        <v>2.6864508934018021</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="65"/>
+      <c r="B107" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C105" s="22">
-        <v>8644.3271284598413</v>
-      </c>
-      <c r="D105" s="34">
-        <v>102218.53437646665</v>
-      </c>
-      <c r="E105" s="23">
-        <f t="shared" si="1"/>
-        <v>8.4567120641968323</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A106" s="73"/>
-      <c r="B106" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C106" s="22">
-        <v>2911.175633376753</v>
-      </c>
-      <c r="D106" s="34">
-        <v>108353.18237297644</v>
-      </c>
-      <c r="E106" s="23">
-        <f t="shared" si="1"/>
-        <v>2.6867467753331145</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A107" s="73"/>
-      <c r="B107" s="21" t="s">
-        <v>11</v>
-      </c>
       <c r="C107" s="22">
-        <v>1261.3670318179013</v>
+        <v>1292.3645450461595</v>
       </c>
       <c r="D107" s="34">
-        <v>114896.8022111171</v>
+        <v>114935.07976390058</v>
       </c>
       <c r="E107" s="26">
-        <f t="shared" si="1"/>
-        <v>1.0978260556809953</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A108" s="72">
+        <v>1.1244300240630904</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="56">
         <v>2024</v>
       </c>
       <c r="B108" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="19">
+        <v>27218.642307488983</v>
+      </c>
+      <c r="D108" s="19">
+        <v>109701.96628582817</v>
+      </c>
+      <c r="E108" s="20">
+        <v>24.81144434236565</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="65"/>
+      <c r="B109" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="22">
+        <v>6490.9179748317247</v>
+      </c>
+      <c r="D109" s="22">
+        <v>113726.4911395112</v>
+      </c>
+      <c r="E109" s="23">
+        <v>5.7074810888776559</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="65"/>
+      <c r="B110" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C108" s="19">
-        <v>27216.220855023865</v>
-      </c>
-      <c r="D108" s="19">
-        <v>109312.18553079128</v>
-      </c>
-      <c r="E108" s="20">
-        <f t="shared" si="1"/>
-        <v>24.897700766725176</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A109" s="73"/>
-      <c r="B109" s="28" t="s">
+      <c r="C110" s="22">
+        <v>3075.0483240757735</v>
+      </c>
+      <c r="D110" s="22">
+        <v>107929.51038394631</v>
+      </c>
+      <c r="E110" s="23">
+        <v>2.8491265392909289</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="65"/>
+      <c r="B111" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C109" s="22">
-        <v>6481.5999923894906</v>
-      </c>
-      <c r="D109" s="22">
-        <v>113253.38418345551</v>
-      </c>
-      <c r="E109" s="23">
-        <f t="shared" si="1"/>
-        <v>5.7230960815176664</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A110" s="73"/>
-      <c r="B110" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C110" s="22">
-        <v>3063.0804967717627</v>
-      </c>
-      <c r="D110" s="22">
-        <v>107330.80483100783</v>
-      </c>
-      <c r="E110" s="23">
-        <f t="shared" si="1"/>
-        <v>2.8538689350131845</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A111" s="73"/>
-      <c r="B111" s="21" t="s">
-        <v>11</v>
-      </c>
       <c r="C111" s="22">
-        <v>1173.8011058394311</v>
+        <v>1184.5630570115904</v>
       </c>
       <c r="D111" s="22">
-        <v>105452.70432413962</v>
+        <v>106065.29210882056</v>
       </c>
       <c r="E111" s="23">
-        <f>C111/D111*100</f>
-        <v>1.1131066892617674</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A112" s="69">
+        <v>1.1168243951058521</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="62">
         <v>2025</v>
       </c>
       <c r="B112" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="19">
+        <v>24061.155692803455</v>
+      </c>
+      <c r="D112" s="19">
+        <v>95142.410341121707</v>
+      </c>
+      <c r="E112" s="20">
+        <v>25.289621743379282</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="63"/>
+      <c r="B113" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="22">
+        <v>13958.56480913311</v>
+      </c>
+      <c r="D113" s="22">
+        <v>100743.19120506106</v>
+      </c>
+      <c r="E113" s="23">
+        <v>13.855591273380142</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="63"/>
+      <c r="B114" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C112" s="19">
-        <v>24411.733749407431</v>
-      </c>
-      <c r="D112" s="19">
-        <v>94718.925535338843</v>
-      </c>
-      <c r="E112" s="20">
-        <f>C112/D112*100</f>
-        <v>25.772815317990084</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A113" s="70"/>
-      <c r="B113" s="21" t="s">
+      <c r="C114" s="22">
+        <v>7886.4657465510445</v>
+      </c>
+      <c r="D114" s="22">
+        <v>104149.13120710102</v>
+      </c>
+      <c r="E114" s="23">
+        <v>7.5722818377320618</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="64"/>
+      <c r="B115" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C113" s="22">
-        <v>13756.152285866512</v>
-      </c>
-      <c r="D113" s="22">
-        <v>100367.3456167377</v>
-      </c>
-      <c r="E113" s="23">
-        <f>C113/D113*100</f>
-        <v>13.705804613380627</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A114" s="70"/>
-      <c r="B114" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C114" s="22">
-        <v>7728.6572601379657</v>
-      </c>
-      <c r="D114" s="22">
-        <v>103593.41079967155</v>
-      </c>
-      <c r="E114" s="23">
-        <f>C114/D114*100</f>
-        <v>7.4605683898984729</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
-      <c r="A115" s="71"/>
-      <c r="B115" s="24" t="s">
-        <v>11</v>
-      </c>
       <c r="C115" s="25">
-        <v>-5025.7739673781398</v>
+        <v>-3989.5060849040219</v>
       </c>
       <c r="D115" s="25">
-        <v>113491.86529323201</v>
+        <v>114040.35138380706</v>
       </c>
       <c r="E115" s="26">
-        <f t="shared" si="1"/>
-        <v>-4.4283120683521338</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
-      <c r="A116" s="37"/>
-      <c r="B116" s="38"/>
-      <c r="C116" s="39"/>
-      <c r="D116" s="39"/>
-      <c r="E116" s="40"/>
-    </row>
-    <row r="117" spans="1:11">
-      <c r="A117" s="41" t="s">
+        <v>-3.4983284745214354</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="56">
+        <v>2026</v>
+      </c>
+      <c r="B116" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="22">
+        <v>28367.342373115553</v>
+      </c>
+      <c r="D116" s="22">
+        <v>107122.68311834852</v>
+      </c>
+      <c r="E116" s="23">
+        <v>26.481172378566619</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="57"/>
+      <c r="B117" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="25">
+        <v>6600.2042668907516</v>
+      </c>
+      <c r="D117" s="25">
+        <v>117761.92281118922</v>
+      </c>
+      <c r="E117" s="26">
+        <v>5.6047015107532108</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
-      <c r="A118" s="41" t="s">
+    <row r="120" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B120" s="66"/>
+      <c r="C120" s="66"/>
+      <c r="D120" s="66"/>
+      <c r="E120" s="66"/>
+      <c r="F120" s="66"/>
+      <c r="G120" s="66"/>
+      <c r="H120" s="66"/>
+      <c r="I120" s="66"/>
+      <c r="J120" s="66"/>
+      <c r="K120" s="66"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="37" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" ht="50.25" customHeight="1">
-      <c r="A119" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="B119" s="75"/>
-      <c r="C119" s="75"/>
-      <c r="D119" s="75"/>
-      <c r="E119" s="75"/>
-      <c r="F119" s="75"/>
-      <c r="G119" s="75"/>
-      <c r="H119" s="75"/>
-      <c r="I119" s="75"/>
-      <c r="J119" s="75"/>
-      <c r="K119" s="75"/>
-    </row>
-    <row r="120" spans="1:11">
-      <c r="A120" s="42"/>
-      <c r="B120" s="43"/>
-      <c r="C120" s="43"/>
-      <c r="D120" s="43"/>
-      <c r="E120" s="43"/>
-    </row>
-    <row r="121" spans="1:11">
-      <c r="A121" s="42"/>
+      <c r="B121" s="37"/>
+      <c r="C121" s="37"/>
+      <c r="D121" s="37"/>
+      <c r="E121" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A119:K119"/>
-    <mergeCell ref="A100:A103"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="A112:A115"/>
+  <mergeCells count="33">
+    <mergeCell ref="A44:A47"/>
     <mergeCell ref="A104:A107"/>
-    <mergeCell ref="A108:A111"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="A96:A99"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="A88:A91"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="A52:A55"/>
-    <mergeCell ref="A12:A15"/>
     <mergeCell ref="A1:XFD3"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A36:A39"/>
     <mergeCell ref="A40:A43"/>
     <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="A120:K120"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="A96:A99"/>
+    <mergeCell ref="A108:A111"/>
+    <mergeCell ref="A112:A115"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5160,488 +4991,494 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29BDEE6-1F24-4BD9-A84D-0A08249D2B36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U40"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="19.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="0.85546875" style="3" customWidth="1"/>
-    <col min="6" max="18" width="11.42578125" style="3" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="3" customWidth="1"/>
-    <col min="20" max="21" width="11.42578125" style="3" customWidth="1"/>
-    <col min="22" max="16384" width="11.42578125" style="3" hidden="1"/>
+    <col min="1" max="1" width="11.375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="0.875" style="3" customWidth="1"/>
+    <col min="6" max="18" width="11.375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="4.75" style="3" customWidth="1"/>
+    <col min="20" max="21" width="11.375" style="3" customWidth="1"/>
+    <col min="22" max="16384" width="11.375" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="62" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A1" s="62" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="62" customFormat="1" ht="18.75" customHeight="1"/>
-    <row r="3" spans="1:5" s="62" customFormat="1" ht="18.75" customHeight="1"/>
-    <row r="4" spans="1:5">
+    <row r="1" spans="1:5" s="67" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="67" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:5" s="67" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="65" t="s">
-        <v>1</v>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="70" t="s">
+        <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="73"/>
+      <c r="B7" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="75"/>
+      <c r="D7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="79"/>
-      <c r="B7" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="61" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="55">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="50">
         <v>1999</v>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="39">
         <v>13960.317834420071</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="39">
         <v>132138.21153868953</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="40">
         <v>10.564936267759721</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="56">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="51">
         <v>2000</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="41">
         <v>18248.688390210074</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="41">
         <v>157518.88517081307</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="42">
         <v>11.585079700393539</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="56">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="51">
         <v>2001</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="41">
         <v>30057.181122777041</v>
       </c>
-      <c r="C10" s="46">
-        <v>156746.29455360502</v>
-      </c>
-      <c r="D10" s="47">
+      <c r="C10" s="41">
+        <v>156746.29455360473</v>
+      </c>
+      <c r="D10" s="42">
         <v>19.17568846420032</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="56">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="51">
         <v>2002</v>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="41">
         <v>24099.206211130102</v>
       </c>
-      <c r="C11" s="46">
-        <v>156689.08687117725</v>
-      </c>
-      <c r="D11" s="47">
+      <c r="C11" s="41">
+        <v>156689.08687117702</v>
+      </c>
+      <c r="D11" s="42">
         <v>15.380271014626198</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="56">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="51">
         <v>2003</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="41">
         <v>18249.968776300091</v>
       </c>
-      <c r="C12" s="46">
-        <v>153816.7425544564</v>
-      </c>
-      <c r="D12" s="47">
+      <c r="C12" s="41">
+        <v>153816.74255445594</v>
+      </c>
+      <c r="D12" s="42">
         <v>11.864747928749713</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="56">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="51">
         <v>2004</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="41">
         <v>25015.569865094192</v>
       </c>
-      <c r="C13" s="46">
-        <v>170254.84761512789</v>
-      </c>
-      <c r="D13" s="47">
+      <c r="C13" s="41">
+        <v>170254.84761512745</v>
+      </c>
+      <c r="D13" s="42">
         <v>14.693014745544028</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="56">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="51">
         <v>2005</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="41">
         <v>25795.824800636266</v>
       </c>
-      <c r="C14" s="46">
-        <v>190325.38256301178</v>
-      </c>
-      <c r="D14" s="47">
+      <c r="C14" s="41">
+        <v>190325.38256301155</v>
+      </c>
+      <c r="D14" s="42">
         <v>13.553538920167924</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="57">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="52">
         <v>2006</v>
       </c>
-      <c r="B15" s="48">
-        <v>21236.848947451224</v>
-      </c>
-      <c r="C15" s="48">
+      <c r="B15" s="43">
+        <v>21236.853631705759</v>
+      </c>
+      <c r="C15" s="43">
         <v>221074.76516866137</v>
       </c>
-      <c r="D15" s="49">
-        <v>9.6061841030337867</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="57">
+      <c r="D15" s="44">
+        <v>9.6061862218891569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="52">
         <v>2007</v>
       </c>
-      <c r="B16" s="48">
-        <v>32394.037818461522</v>
-      </c>
-      <c r="C16" s="48">
+      <c r="B16" s="43">
+        <v>32394.040099684174</v>
+      </c>
+      <c r="C16" s="43">
         <v>246538.83174366935</v>
       </c>
-      <c r="D16" s="49">
-        <v>13.139527590583441</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="57">
+      <c r="D16" s="44">
+        <v>13.139528515882972</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="52">
         <v>2008</v>
       </c>
-      <c r="B17" s="48">
-        <v>29521.419070842763</v>
-      </c>
-      <c r="C17" s="48">
+      <c r="B17" s="43">
+        <v>29522.229957149058</v>
+      </c>
+      <c r="C17" s="43">
         <v>274661.96495037084</v>
       </c>
-      <c r="D17" s="49">
-        <v>10.74827345540073</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="57">
+      <c r="D17" s="44">
+        <v>10.74856868605141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="52">
         <v>2009</v>
       </c>
-      <c r="B18" s="48">
-        <v>17851.259975357607</v>
-      </c>
-      <c r="C18" s="48">
+      <c r="B18" s="43">
+        <v>17851.260299611902</v>
+      </c>
+      <c r="C18" s="43">
         <v>215557.50457752484</v>
       </c>
-      <c r="D18" s="49">
-        <v>8.281437480149263</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="57">
+      <c r="D18" s="44">
+        <v>8.2814376305751551</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="52">
         <v>2010</v>
       </c>
-      <c r="B19" s="48">
-        <v>27199.001574955291</v>
-      </c>
-      <c r="C19" s="48">
+      <c r="B19" s="43">
+        <v>27199.002382002123</v>
+      </c>
+      <c r="C19" s="43">
         <v>249641.60365031241</v>
       </c>
-      <c r="D19" s="49">
-        <v>10.895219858086845</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="57">
+      <c r="D19" s="44">
+        <v>10.89522018136903</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="52">
         <v>2011</v>
       </c>
-      <c r="B20" s="48">
-        <v>25632.564790888606</v>
-      </c>
-      <c r="C20" s="48">
-        <v>287367.3214799345</v>
-      </c>
-      <c r="D20" s="49">
-        <v>8.9197911087737953</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="57">
+      <c r="B20" s="43">
+        <v>25632.578587052813</v>
+      </c>
+      <c r="C20" s="43">
+        <v>287367.32146159705</v>
+      </c>
+      <c r="D20" s="44">
+        <v>8.9197959102243569</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="52">
         <v>2012</v>
       </c>
-      <c r="B21" s="48">
-        <v>21769.332132260963</v>
-      </c>
-      <c r="C21" s="48">
-        <v>297492.11822708906</v>
-      </c>
-      <c r="D21" s="49">
-        <v>7.3176164336708425</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="57">
+      <c r="B21" s="43">
+        <v>21770.129704685518</v>
+      </c>
+      <c r="C21" s="43">
+        <v>297492.11820970633</v>
+      </c>
+      <c r="D21" s="44">
+        <v>7.3178845327725464</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="52">
         <v>2013</v>
       </c>
-      <c r="B22" s="48">
-        <v>48356.760011782091</v>
-      </c>
-      <c r="C22" s="48">
-        <v>291886.29979193193</v>
-      </c>
-      <c r="D22" s="49">
-        <v>16.566985174108101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="57">
+      <c r="B22" s="43">
+        <v>48357.108387334752</v>
+      </c>
+      <c r="C22" s="43">
+        <v>291886.2997611821</v>
+      </c>
+      <c r="D22" s="44">
+        <v>16.567104529023787</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="52">
         <v>2014</v>
       </c>
-      <c r="B23" s="48">
-        <v>30351.497115624894</v>
-      </c>
-      <c r="C23" s="48">
-        <v>295110.43902960944</v>
-      </c>
-      <c r="D23" s="49">
-        <v>10.28479277636791</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="57">
+      <c r="B23" s="43">
+        <v>30352.408991116659</v>
+      </c>
+      <c r="C23" s="43">
+        <v>295110.438988176</v>
+      </c>
+      <c r="D23" s="44">
+        <v>10.285101772469922</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="52">
         <v>2015</v>
       </c>
-      <c r="B24" s="48">
-        <v>35945.172957005554</v>
-      </c>
-      <c r="C24" s="48">
-        <v>280239.7213382062</v>
-      </c>
-      <c r="D24" s="49">
-        <v>12.826580323931047</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="57">
+      <c r="B24" s="43">
+        <v>35945.607983971015</v>
+      </c>
+      <c r="C24" s="43">
+        <v>280239.72162319778</v>
+      </c>
+      <c r="D24" s="44">
+        <v>12.826735544757085</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="52">
         <v>2016</v>
       </c>
-      <c r="B25" s="48">
-        <v>31192.304756424597</v>
-      </c>
-      <c r="C25" s="48">
-        <v>263096.54087677394</v>
-      </c>
-      <c r="D25" s="49">
-        <v>11.855839933309531</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="57">
+      <c r="B25" s="43">
+        <v>31192.354981810626</v>
+      </c>
+      <c r="C25" s="43">
+        <v>263096.53994863929</v>
+      </c>
+      <c r="D25" s="44">
+        <v>11.855859065231295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="52">
         <v>2017</v>
       </c>
-      <c r="B26" s="48">
-        <v>34041.823482311593</v>
-      </c>
-      <c r="C26" s="48">
-        <v>277379.10831067228</v>
-      </c>
-      <c r="D26" s="49">
-        <v>12.272670313794436</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="57">
+      <c r="B26" s="43">
+        <v>34064.567813291651</v>
+      </c>
+      <c r="C26" s="43">
+        <v>277379.10714489641</v>
+      </c>
+      <c r="D26" s="44">
+        <v>12.280870092893158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="52">
         <v>2018</v>
       </c>
-      <c r="B27" s="48">
-        <v>34110.911240511574</v>
-      </c>
-      <c r="C27" s="48">
-        <v>289586.73150372063</v>
-      </c>
-      <c r="D27" s="49">
-        <v>11.779169253848675</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="57">
+      <c r="B27" s="43">
+        <v>34114.123374415576</v>
+      </c>
+      <c r="C27" s="43">
+        <v>289586.7265983565</v>
+      </c>
+      <c r="D27" s="44">
+        <v>11.780278666477106</v>
+      </c>
+      <c r="F27" s="55"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="52">
         <v>2019</v>
       </c>
-      <c r="B28" s="48">
-        <v>34619.748358263721</v>
-      </c>
-      <c r="C28" s="48">
-        <v>282669.49695353978</v>
-      </c>
-      <c r="D28" s="49">
-        <v>12.247429854079341</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="51">
+      <c r="B28" s="43">
+        <v>34798.52503376481</v>
+      </c>
+      <c r="C28" s="43">
+        <v>282669.49861239223</v>
+      </c>
+      <c r="D28" s="44">
+        <v>12.310675613955063</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="3">
         <v>2020</v>
       </c>
-      <c r="B29" s="48">
-        <v>28215.286421661629</v>
-      </c>
-      <c r="C29" s="48">
-        <v>227344.66267409135</v>
-      </c>
-      <c r="D29" s="49">
-        <v>12.410797812354843</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="51">
+      <c r="B29" s="43">
+        <v>28284.24603275066</v>
+      </c>
+      <c r="C29" s="43">
+        <v>227344.6960643442</v>
+      </c>
+      <c r="D29" s="44">
+        <v>12.441128613242649</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="3">
         <v>2021</v>
       </c>
-      <c r="B30" s="48">
-        <v>33847.015206203112</v>
-      </c>
-      <c r="C30" s="48">
-        <v>280328.79800906545</v>
-      </c>
-      <c r="D30" s="49">
-        <v>12.074041427990764</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="51">
+      <c r="B30" s="43">
+        <v>33855.04715845616</v>
+      </c>
+      <c r="C30" s="43">
+        <v>280328.98189442267</v>
+      </c>
+      <c r="D30" s="44">
+        <v>12.076898695835391</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3">
         <v>2022</v>
       </c>
-      <c r="B31" s="48">
-        <v>36419.45219572213</v>
-      </c>
-      <c r="C31" s="48">
-        <v>329359.17609245755</v>
-      </c>
-      <c r="D31" s="49">
-        <v>11.057670421636736</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="51">
+      <c r="B31" s="43">
+        <v>36420.58194170786</v>
+      </c>
+      <c r="C31" s="43">
+        <v>329359.95043519867</v>
+      </c>
+      <c r="D31" s="44">
+        <v>11.057987437022518</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3">
         <v>2023</v>
       </c>
-      <c r="B32" s="48">
-        <v>36475.534208166027</v>
-      </c>
-      <c r="C32" s="48">
-        <v>418991.6463862292</v>
-      </c>
-      <c r="D32" s="49">
-        <v>8.7055516554481969</v>
-      </c>
-      <c r="F32" s="53"/>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="51">
+      <c r="B32" s="43">
+        <v>36507.390076674666</v>
+      </c>
+      <c r="C32" s="43">
+        <v>419191.81597182376</v>
+      </c>
+      <c r="D32" s="44">
+        <v>8.7089939940832561</v>
+      </c>
+      <c r="F32" s="47"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="53">
         <v>2024</v>
       </c>
-      <c r="B33" s="48">
-        <v>37934.702450024553</v>
-      </c>
-      <c r="C33" s="48">
-        <v>435349.07886939426</v>
-      </c>
-      <c r="D33" s="49">
-        <v>8.7136287386989171</v>
-      </c>
-      <c r="F33" s="59"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="58">
+      <c r="B33" s="43">
+        <v>37969.171663408073</v>
+      </c>
+      <c r="C33" s="43">
+        <v>437423.25991810625</v>
+      </c>
+      <c r="D33" s="44">
+        <v>8.6801903653949744</v>
+      </c>
+      <c r="F33" s="47"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="54">
         <v>2025</v>
       </c>
-      <c r="B34" s="50">
-        <v>40870.76932803377</v>
-      </c>
-      <c r="C34" s="50">
-        <v>420755.81887394178</v>
-      </c>
-      <c r="D34" s="60">
-        <v>9.9159608665907353</v>
-      </c>
-      <c r="F34" s="59"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="51"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="53"/>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="41" t="s">
+      <c r="B34" s="45">
+        <v>41916.680163583587</v>
+      </c>
+      <c r="C34" s="45">
+        <v>414075.08413709089</v>
+      </c>
+      <c r="D34" s="49">
+        <v>10.122966043932729</v>
+      </c>
+      <c r="F34" s="47"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="47"/>
+    </row>
+    <row r="36" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="47"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="41" t="s">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:11" ht="45.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="66"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="37" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="63.75" customHeight="1">
-      <c r="A38" s="75" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="75"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75"/>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="42"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="54"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="48"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
     </row>
@@ -5659,91 +5496,81 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99D62C68-BFFF-45D5-A77D-FEEE04CC812E}">
-  <dimension ref="A1:I73"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="12" customHeight="1" zeroHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="11.4" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="11.42578125" customWidth="1"/>
-    <col min="10" max="11" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" hidden="1"/>
+    <col min="1" max="9" width="11.375" customWidth="1"/>
+    <col min="10" max="16384" width="11.375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60" ht="12" customHeight="1"/>
-    <row r="61" ht="12" customHeight="1"/>
-    <row r="62" ht="12" customHeight="1"/>
-    <row r="63" ht="12" customHeight="1"/>
-    <row r="64" ht="12" customHeight="1"/>
-    <row r="65" ht="12" customHeight="1"/>
-    <row r="66" ht="12" customHeight="1"/>
-    <row r="67" ht="12" customHeight="1"/>
-    <row r="68" ht="12" customHeight="1"/>
-    <row r="69" ht="12" customHeight="1"/>
-    <row r="70" ht="12" customHeight="1"/>
-    <row r="71" ht="12" customHeight="1"/>
-    <row r="72" ht="12" customHeight="1"/>
-    <row r="73" ht="12" customHeight="1"/>
+    <row r="1" x14ac:dyDescent="0.2"/>
+    <row r="2" x14ac:dyDescent="0.2"/>
+    <row r="3" x14ac:dyDescent="0.2"/>
+    <row r="4" x14ac:dyDescent="0.2"/>
+    <row r="5" x14ac:dyDescent="0.2"/>
+    <row r="6" x14ac:dyDescent="0.2"/>
+    <row r="7" x14ac:dyDescent="0.2"/>
+    <row r="8" x14ac:dyDescent="0.2"/>
+    <row r="9" x14ac:dyDescent="0.2"/>
+    <row r="10" x14ac:dyDescent="0.2"/>
+    <row r="11" x14ac:dyDescent="0.2"/>
+    <row r="12" x14ac:dyDescent="0.2"/>
+    <row r="13" x14ac:dyDescent="0.2"/>
+    <row r="14" x14ac:dyDescent="0.2"/>
+    <row r="15" x14ac:dyDescent="0.2"/>
+    <row r="16" x14ac:dyDescent="0.2"/>
+    <row r="17" x14ac:dyDescent="0.2"/>
+    <row r="18" x14ac:dyDescent="0.2"/>
+    <row r="19" x14ac:dyDescent="0.2"/>
+    <row r="20" x14ac:dyDescent="0.2"/>
+    <row r="21" x14ac:dyDescent="0.2"/>
+    <row r="22" x14ac:dyDescent="0.2"/>
+    <row r="23" x14ac:dyDescent="0.2"/>
+    <row r="24" x14ac:dyDescent="0.2"/>
+    <row r="25" x14ac:dyDescent="0.2"/>
+    <row r="26" x14ac:dyDescent="0.2"/>
+    <row r="27" x14ac:dyDescent="0.2"/>
+    <row r="28" x14ac:dyDescent="0.2"/>
+    <row r="29" x14ac:dyDescent="0.2"/>
+    <row r="30" x14ac:dyDescent="0.2"/>
+    <row r="31" x14ac:dyDescent="0.2"/>
+    <row r="32" x14ac:dyDescent="0.2"/>
+    <row r="33" x14ac:dyDescent="0.2"/>
+    <row r="34" x14ac:dyDescent="0.2"/>
+    <row r="35" x14ac:dyDescent="0.2"/>
+    <row r="36" x14ac:dyDescent="0.2"/>
+    <row r="37" x14ac:dyDescent="0.2"/>
+    <row r="38" x14ac:dyDescent="0.2"/>
+    <row r="39" x14ac:dyDescent="0.2"/>
+    <row r="40" x14ac:dyDescent="0.2"/>
+    <row r="41" x14ac:dyDescent="0.2"/>
+    <row r="42" x14ac:dyDescent="0.2"/>
+    <row r="43" x14ac:dyDescent="0.2"/>
+    <row r="44" x14ac:dyDescent="0.2"/>
+    <row r="45" x14ac:dyDescent="0.2"/>
+    <row r="46" x14ac:dyDescent="0.2"/>
+    <row r="47" x14ac:dyDescent="0.2"/>
+    <row r="48" x14ac:dyDescent="0.2"/>
+    <row r="49" x14ac:dyDescent="0.2"/>
+    <row r="50" x14ac:dyDescent="0.2"/>
+    <row r="51" x14ac:dyDescent="0.2"/>
+    <row r="52" x14ac:dyDescent="0.2"/>
+    <row r="53" x14ac:dyDescent="0.2"/>
+    <row r="54" x14ac:dyDescent="0.2"/>
+    <row r="55" x14ac:dyDescent="0.2"/>
+    <row r="56" x14ac:dyDescent="0.2"/>
+    <row r="57" x14ac:dyDescent="0.2"/>
+    <row r="58" x14ac:dyDescent="0.2"/>
+    <row r="59" x14ac:dyDescent="0.2"/>
+    <row r="60" x14ac:dyDescent="0.2"/>
+    <row r="61" x14ac:dyDescent="0.2"/>
+    <row r="62" x14ac:dyDescent="0.2"/>
+    <row r="63" x14ac:dyDescent="0.2"/>
+    <row r="64" x14ac:dyDescent="0.2"/>
+    <row r="65" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>